--- a/data/exports/reporting/daily_lottery_summary.xlsx
+++ b/data/exports/reporting/daily_lottery_summary.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:44</t>
+          <t>2026-05-24 05:37:17</t>
         </is>
       </c>
     </row>
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12703</v>
+        <v>12709</v>
       </c>
     </row>
     <row r="4">
@@ -480,7 +480,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -654,32 +654,32 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J2" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K2" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>474917.1</v>
+        <v>364517.7</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -691,49 +691,51 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PowerBall Plus</t>
+          <t>Lotto Plus 2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Plus 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I3" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J3" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K3" t="n">
-        <v>48</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>33</v>
+      </c>
+      <c r="L3" t="n">
+        <v>47</v>
+      </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>96000000</v>
+        <v>8500000</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -749,12 +751,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -764,34 +766,36 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="I4" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="J4" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="K4" t="n">
-        <v>25</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="L4" t="n">
+        <v>53</v>
+      </c>
       <c r="M4" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="N4" t="n">
-        <v>100000000</v>
+        <v>10500000</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -807,49 +811,57 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto Plus 1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" s="1" t="n">
-        <v>46163</v>
+        <v>46165</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J5" t="n">
         <v>27</v>
       </c>
       <c r="K5" t="n">
-        <v>28</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="L5" t="n">
+        <v>41</v>
+      </c>
+      <c r="M5" t="n">
+        <v>52</v>
+      </c>
       <c r="N5" t="n">
-        <v>345741</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
+        <v>6000000</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -864,43 +876,43 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J6" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L6" t="n">
         <v>46</v>
       </c>
       <c r="M6" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -918,43 +930,43 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M7" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -982,32 +994,32 @@
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I8" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J8" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>340306.8</v>
+        <v>474917.1</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1019,51 +1031,55 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>PowerBall Plus</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H9" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I9" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="J9" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="K9" t="n">
         <v>48</v>
       </c>
-      <c r="L9" t="n">
-        <v>49</v>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>16</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="N9" t="n">
+        <v>96000000</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1073,51 +1089,55 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J10" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="K10" t="n">
-        <v>44</v>
-      </c>
-      <c r="L10" t="n">
-        <v>45</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>13</v>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="N10" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1127,12 +1147,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1142,42 +1162,34 @@
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="K11" t="n">
-        <v>24</v>
-      </c>
-      <c r="L11" t="n">
-        <v>58</v>
-      </c>
-      <c r="M11" t="n">
-        <v>53</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>8500000</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>345741</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1187,57 +1199,51 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lotto Plus 2</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plus 2</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I12" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="L12" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="M12" t="n">
-        <v>28</v>
-      </c>
-      <c r="N12" t="n">
-        <v>7500000</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1247,57 +1253,51 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lotto Plus 1</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plus 1</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" t="n">
+        <v>12</v>
+      </c>
+      <c r="J13" t="n">
+        <v>26</v>
+      </c>
+      <c r="K13" t="n">
+        <v>42</v>
+      </c>
+      <c r="L13" t="n">
         <v>46</v>
       </c>
-      <c r="I13" t="n">
-        <v>47</v>
-      </c>
-      <c r="J13" t="n">
-        <v>51</v>
-      </c>
-      <c r="K13" t="n">
-        <v>54</v>
-      </c>
-      <c r="L13" t="n">
-        <v>55</v>
-      </c>
       <c r="M13" t="n">
-        <v>41</v>
-      </c>
-      <c r="N13" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1322,32 +1322,32 @@
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I14" t="n">
+        <v>14</v>
+      </c>
+      <c r="J14" t="n">
+        <v>20</v>
+      </c>
+      <c r="K14" t="n">
         <v>21</v>
-      </c>
-      <c r="J14" t="n">
-        <v>27</v>
-      </c>
-      <c r="K14" t="n">
-        <v>30</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
-        <v>394608</v>
+        <v>340306.8</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -1359,49 +1359,51 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PowerBall Plus</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J15" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>43</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="L15" t="n">
+        <v>58</v>
+      </c>
       <c r="M15" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="N15" t="n">
-        <v>93000000</v>
+        <v>8500000</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1417,51 +1419,57 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>Lotto Plus 1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Plus 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H16" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="I16" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="J16" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="K16" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="L16" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="M16" t="n">
-        <v>15</v>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="N16" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1471,51 +1479,57 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>Lotto Plus 2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Plus 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I17" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K17" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L17" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="M17" t="n">
-        <v>18</v>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="N17" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1525,55 +1539,51 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>9</v>
+      </c>
+      <c r="H18" t="n">
         <v>19</v>
       </c>
-      <c r="H18" t="n">
-        <v>24</v>
-      </c>
       <c r="I18" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J18" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="K18" t="n">
         <v>48</v>
       </c>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>49</v>
+      </c>
       <c r="M18" t="n">
-        <v>4</v>
-      </c>
-      <c r="N18" t="n">
-        <v>91000000</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1583,48 +1593,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" s="1" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H19" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I19" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J19" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K19" t="n">
-        <v>32</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="n">
-        <v>300000</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="L19" t="n">
+        <v>45</v>
+      </c>
+      <c r="M19" t="n">
+        <v>13</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -1640,43 +1652,43 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H20" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I20" t="n">
+        <v>27</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34</v>
+      </c>
+      <c r="K20" t="n">
+        <v>37</v>
+      </c>
+      <c r="L20" t="n">
+        <v>39</v>
+      </c>
+      <c r="M20" t="n">
         <v>18</v>
-      </c>
-      <c r="J20" t="n">
-        <v>19</v>
-      </c>
-      <c r="K20" t="n">
-        <v>26</v>
-      </c>
-      <c r="L20" t="n">
-        <v>33</v>
-      </c>
-      <c r="M20" t="n">
-        <v>37</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -1694,43 +1706,43 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" t="n">
         <v>8</v>
       </c>
-      <c r="H21" t="n">
-        <v>17</v>
-      </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K21" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L21" t="n">
         <v>49</v>
       </c>
       <c r="M21" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -1743,49 +1755,55 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall Plus</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" s="1" t="n">
-        <v>46159</v>
+        <v>46161</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H22" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I22" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="K22" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>11</v>
+      </c>
       <c r="N22" t="n">
-        <v>262006.6</v>
-      </c>
-      <c r="O22" t="inlineStr"/>
+        <v>93000000</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1795,51 +1813,55 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" s="1" t="n">
-        <v>46159</v>
+        <v>46161</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H23" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="I23" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="J23" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="K23" t="n">
-        <v>27</v>
-      </c>
-      <c r="L23" t="n">
-        <v>40</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
-        <v>12</v>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="N23" t="n">
+        <v>91000000</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1849,50 +1871,48 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" s="1" t="n">
-        <v>46159</v>
+        <v>46161</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H24" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I24" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K24" t="n">
-        <v>24</v>
-      </c>
-      <c r="L24" t="n">
-        <v>49</v>
-      </c>
-      <c r="M24" t="n">
-        <v>10</v>
-      </c>
-      <c r="N24" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="n">
+        <v>394608</v>
+      </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -1903,57 +1923,49 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lotto Plus 2</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Plus 2</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" s="1" t="n">
-        <v>46158</v>
+        <v>46160</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H25" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="K25" t="n">
-        <v>25</v>
-      </c>
-      <c r="L25" t="n">
-        <v>36</v>
-      </c>
-      <c r="M25" t="n">
-        <v>11</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>300000</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1968,43 +1980,43 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" s="1" t="n">
-        <v>46158</v>
+        <v>46160</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I26" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J26" t="n">
         <v>19</v>
       </c>
       <c r="K26" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L26" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="M26" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
@@ -2246,7 +2258,7 @@
         <v>8</v>
       </c>
       <c r="Y2" t="n">
-        <v>73.86</v>
+        <v>73.84</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -2255,7 +2267,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -2287,32 +2299,32 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
         <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
         <v>25</v>
       </c>
       <c r="L3" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -2336,16 +2348,16 @@
         <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>47.86</v>
+        <v>47.84</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3|10|14|25|35</t>
+          <t>6|10|12|25|27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -2377,23 +2389,23 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
         <v>10</v>
       </c>
-      <c r="I4" t="n">
-        <v>12</v>
-      </c>
       <c r="J4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -2402,7 +2414,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -2426,16 +2438,16 @@
         <v>5</v>
       </c>
       <c r="Y4" t="n">
-        <v>42.86</v>
+        <v>42.84</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10|12|15|21|25</t>
+          <t>3|10|14|25|35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -2467,23 +2479,23 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K5" t="n">
+        <v>21</v>
+      </c>
+      <c r="L5" t="n">
         <v>25</v>
-      </c>
-      <c r="L5" t="n">
-        <v>35</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -2492,7 +2504,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -2516,16 +2528,16 @@
         <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>40.36</v>
+        <v>40.34</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4|7|10|25|35</t>
+          <t>10|12|15|21|25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -2569,11 +2581,11 @@
         <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
@@ -2582,7 +2594,7 @@
         <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -2606,16 +2618,16 @@
         <v>5</v>
       </c>
       <c r="Y6" t="n">
-        <v>38.86</v>
+        <v>38.84</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4|6|10|25|27</t>
+          <t>4|6|10|25|35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -2647,23 +2659,23 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
         <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L7" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -2696,16 +2708,16 @@
         <v>5</v>
       </c>
       <c r="Y7" t="n">
-        <v>37.86</v>
+        <v>37.84</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9|10|14|25|31</t>
+          <t>5|10|12|23|27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -2737,23 +2749,23 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J8" t="n">
         <v>10</v>
       </c>
-      <c r="J8" t="n">
-        <v>14</v>
-      </c>
       <c r="K8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="O8" t="n">
         <v>3</v>
@@ -2762,7 +2774,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -2786,16 +2798,16 @@
         <v>5</v>
       </c>
       <c r="Y8" t="n">
-        <v>37.14571428571428</v>
+        <v>37.12571428571429</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7|10|14|23|25</t>
+          <t>3|8|10|25|27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -2827,32 +2839,32 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
         <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
         <v>25</v>
       </c>
       <c r="L9" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="n">
         <v>2</v>
       </c>
-      <c r="P9" t="n">
-        <v>3</v>
-      </c>
       <c r="Q9" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -2876,16 +2888,16 @@
         <v>5</v>
       </c>
       <c r="Y9" t="n">
-        <v>36.61</v>
+        <v>36.59</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6|10|15|25|36</t>
+          <t>9|10|14|25|31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -2920,20 +2932,20 @@
         <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="K10" t="n">
         <v>25</v>
       </c>
       <c r="L10" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -2942,7 +2954,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -2966,16 +2978,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>36.19333333333333</v>
+        <v>36.17333333333333</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4|14|17|25|35</t>
+          <t>4|6|9|25|27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -3007,23 +3019,23 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J11" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K11" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -3032,7 +3044,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -3056,16 +3068,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>35.86</v>
+        <v>35.84</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6|10|11|21|25</t>
+          <t>4|14|17|25|35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -3100,29 +3112,29 @@
         <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
+        <v>23</v>
+      </c>
+      <c r="L12" t="n">
         <v>25</v>
-      </c>
-      <c r="L12" t="n">
-        <v>35</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
@@ -3146,16 +3158,16 @@
         <v>5</v>
       </c>
       <c r="Y12" t="n">
-        <v>35.58727272727273</v>
+        <v>35.56727272727272</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4|6|13|25|35</t>
+          <t>4|10|14|23|25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr"/>
@@ -3202,7 +3214,7 @@
         <v>47</v>
       </c>
       <c r="M13" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="N13" t="n">
         <v>156</v>
@@ -3238,16 +3250,16 @@
         <v>8</v>
       </c>
       <c r="Y13" t="n">
-        <v>73.72</v>
+        <v>73.81</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2|6|8|44|47|49|7</t>
+          <t>2|6|8|44|47|49|23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -3332,7 +3344,7 @@
         <v>5</v>
       </c>
       <c r="Y14" t="n">
-        <v>47.72</v>
+        <v>47.81</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
@@ -3341,7 +3353,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -3378,22 +3390,22 @@
         <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K15" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="L15" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M15" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="N15" t="n">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="O15" t="n">
         <v>3</v>
@@ -3402,7 +3414,7 @@
         <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -3423,23 +3435,23 @@
         <v>0.5</v>
       </c>
       <c r="X15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="n">
-        <v>45.72</v>
+        <v>42.81</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2|8|29|33|44|49|19</t>
+          <t>2|17|23|27|40|44|32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16">
@@ -3466,28 +3478,28 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
         <v>8</v>
       </c>
       <c r="J16" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="K16" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="L16" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M16" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="N16" t="n">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
@@ -3496,7 +3508,7 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
@@ -3505,7 +3517,7 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -3517,23 +3529,23 @@
         <v>0.5</v>
       </c>
       <c r="X16" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y16" t="n">
-        <v>40.72</v>
+        <v>40.31</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2|8|17|20|33|49|28</t>
+          <t>4|8|29|33|35|44|13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17">
@@ -3560,13 +3572,13 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J17" t="n">
         <v>29</v>
@@ -3575,13 +3587,13 @@
         <v>33</v>
       </c>
       <c r="L17" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M17" t="n">
         <v>13</v>
       </c>
       <c r="N17" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="O17" t="n">
         <v>3</v>
@@ -3590,7 +3602,7 @@
         <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -3599,7 +3611,7 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -3614,20 +3626,20 @@
         <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>40.22</v>
+        <v>38.81</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>4|8|29|33|35|44|13</t>
+          <t>2|7|29|33|40|46|13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18">
@@ -3654,16 +3666,16 @@
         </is>
       </c>
       <c r="G18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" t="n">
         <v>4</v>
       </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J18" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="K18" t="n">
         <v>33</v>
@@ -3672,10 +3684,10 @@
         <v>40</v>
       </c>
       <c r="M18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N18" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="O18" t="n">
         <v>3</v>
@@ -3684,7 +3696,7 @@
         <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -3693,7 +3705,7 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -3708,20 +3720,20 @@
         <v>5</v>
       </c>
       <c r="Y18" t="n">
-        <v>38.72</v>
+        <v>37.81</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1|16|17|33|40|42|18</t>
+          <t>4|8|27|33|40|43|20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19">
@@ -3751,34 +3763,34 @@
         <v>6</v>
       </c>
       <c r="H19" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K19" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="L19" t="n">
+        <v>40</v>
+      </c>
+      <c r="M19" t="n">
+        <v>18</v>
+      </c>
+      <c r="N19" t="n">
+        <v>149</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q19" t="n">
         <v>41</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>153</v>
-      </c>
-      <c r="O19" t="n">
-        <v>3</v>
-      </c>
-      <c r="P19" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>33</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
@@ -3802,20 +3814,20 @@
         <v>5</v>
       </c>
       <c r="Y19" t="n">
-        <v>37.00571428571428</v>
+        <v>37.09571428571429</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11|14|20|23|41|44|1</t>
+          <t>1|16|17|33|40|42|18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -3845,25 +3857,25 @@
         <v>7</v>
       </c>
       <c r="H20" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J20" t="n">
         <v>27</v>
       </c>
       <c r="K20" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L20" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="M20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N20" t="n">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="O20" t="n">
         <v>3</v>
@@ -3872,7 +3884,7 @@
         <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
@@ -3896,20 +3908,20 @@
         <v>5</v>
       </c>
       <c r="Y20" t="n">
-        <v>36.47</v>
+        <v>36.56</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11|20|27|30|31|44|7</t>
+          <t>1|8|27|32|42|45|10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21">
@@ -3942,22 +3954,22 @@
         <v>8</v>
       </c>
       <c r="I21" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="K21" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L21" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M21" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="N21" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="O21" t="n">
         <v>3</v>
@@ -3966,7 +3978,7 @@
         <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
@@ -3990,20 +4002,20 @@
         <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>36.05333333333333</v>
+        <v>36.14333333333333</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>8|23|26|32|37|41|11</t>
+          <t>8|17|19|30|42|49|24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22">
@@ -4033,25 +4045,25 @@
         <v>9</v>
       </c>
       <c r="H22" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K22" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="L22" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="M22" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="N22" t="n">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="O22" t="n">
         <v>3</v>
@@ -4060,7 +4072,7 @@
         <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
@@ -4084,20 +4096,20 @@
         <v>5</v>
       </c>
       <c r="Y22" t="n">
-        <v>35.72</v>
+        <v>35.81</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>8|11|14|30|31|33|49</t>
+          <t>2|3|24|43|44|47|10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB22" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23">
@@ -4130,10 +4142,10 @@
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J23" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="K23" t="n">
         <v>30</v>
@@ -4142,10 +4154,10 @@
         <v>32</v>
       </c>
       <c r="M23" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="N23" t="n">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="O23" t="n">
         <v>3</v>
@@ -4154,7 +4166,7 @@
         <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R23" t="n">
         <v>1</v>
@@ -4178,20 +4190,20 @@
         <v>5</v>
       </c>
       <c r="Y23" t="n">
-        <v>35.44727272727273</v>
+        <v>35.53727272727272</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1|9|27|30|32|46|18</t>
+          <t>1|13|14|30|32|47|21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB23" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24">
@@ -4281,7 +4293,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -4373,7 +4385,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -4465,7 +4477,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -4557,7 +4569,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -4649,7 +4661,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -4741,7 +4753,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -4833,7 +4845,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -4925,7 +4937,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -5017,7 +5029,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -5109,7 +5121,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -5160,7 +5172,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -5200,12 +5212,12 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|19</t>
+          <t>1|3|5|44|46|49|2</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -5258,7 +5270,7 @@
         <v>46</v>
       </c>
       <c r="M35" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="N35" t="n">
         <v>148</v>
@@ -5298,12 +5310,12 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|19</t>
+          <t>1|3|5|44|46|49|2</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB35" t="n">
@@ -5341,25 +5353,25 @@
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I36" t="n">
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K36" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L36" t="n">
         <v>38</v>
       </c>
       <c r="M36" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N36" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -5368,7 +5380,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -5396,16 +5408,16 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>5|19|22|26|38|45|30</t>
+          <t>17|19|20|31|38|44|15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37">
@@ -5436,7 +5448,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H37" t="n">
         <v>1</v>
@@ -5445,19 +5457,19 @@
         <v>2</v>
       </c>
       <c r="J37" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K37" t="n">
+        <v>33</v>
+      </c>
+      <c r="L37" t="n">
         <v>42</v>
       </c>
-      <c r="L37" t="n">
-        <v>45</v>
-      </c>
       <c r="M37" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="N37" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -5475,7 +5487,7 @@
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -5490,16 +5502,16 @@
         <v>8</v>
       </c>
       <c r="Y37" t="n">
-        <v>39.1667</v>
+        <v>38.80955714285714</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>1|2|20|42|45|49|10</t>
+          <t>1|2|24|33|42|49|23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB37" t="n">
@@ -5537,25 +5549,25 @@
         <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I38" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J38" t="n">
         <v>24</v>
       </c>
       <c r="K38" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L38" t="n">
         <v>41</v>
       </c>
       <c r="M38" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="N38" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -5564,7 +5576,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -5592,16 +5604,16 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>6|16|24|31|41|45|12</t>
+          <t>5|13|24|30|41|48|47</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39">
@@ -5632,28 +5644,28 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J39" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="K39" t="n">
         <v>38</v>
       </c>
       <c r="L39" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="M39" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="N39" t="n">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -5662,7 +5674,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -5671,7 +5683,7 @@
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -5683,19 +5695,19 @@
         <v>0.5</v>
       </c>
       <c r="X39" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.80955714285714</v>
+        <v>36.1667</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>1|3|6|38|48|49|15</t>
+          <t>3|8|23|38|44|49|39</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB39" t="n">
@@ -5793,7 +5805,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB40" t="n">
@@ -5828,28 +5840,28 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I41" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J41" t="n">
         <v>20</v>
       </c>
       <c r="K41" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L41" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M41" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="N41" t="n">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -5858,7 +5870,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -5867,7 +5879,7 @@
         <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -5879,19 +5891,19 @@
         <v>0.5</v>
       </c>
       <c r="X41" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>38.6667</v>
+        <v>35.97439230769231</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>1|9|20|38|42|49|8</t>
+          <t>6|11|20|39|44|49|40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB41" t="n">
@@ -5932,22 +5944,22 @@
         <v>9</v>
       </c>
       <c r="I42" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J42" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="K42" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="L42" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M42" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="N42" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -5956,7 +5968,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -5984,16 +5996,16 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>9|19|24|26|45|46|17</t>
+          <t>9|11|14|40|44|45|37</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43">
@@ -6024,28 +6036,28 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J43" t="n">
         <v>24</v>
       </c>
       <c r="K43" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="L43" t="n">
         <v>38</v>
       </c>
       <c r="M43" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="N43" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -6054,7 +6066,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -6063,7 +6075,7 @@
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -6075,23 +6087,23 @@
         <v>0.5</v>
       </c>
       <c r="X43" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>38.33336666666666</v>
+        <v>35.6667</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>1|2|24|29|38|49|7</t>
+          <t>3|5|24|37|38|44|19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44">
@@ -6125,22 +6137,22 @@
         <v>5</v>
       </c>
       <c r="H44" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J44" t="n">
         <v>24</v>
       </c>
       <c r="K44" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L44" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M44" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="N44" t="n">
         <v>163</v>
@@ -6180,16 +6192,16 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>5|13|24|32|41|48|18</t>
+          <t>2|9|24|40|43|45|34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45">
@@ -6220,28 +6232,28 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H45" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I45" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J45" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K45" t="n">
+        <v>29</v>
+      </c>
+      <c r="L45" t="n">
         <v>38</v>
       </c>
-      <c r="L45" t="n">
-        <v>48</v>
-      </c>
       <c r="M45" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="N45" t="n">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="O45" t="n">
         <v>3</v>
@@ -6250,7 +6262,7 @@
         <v>3</v>
       </c>
       <c r="Q45" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="R45" t="n">
         <v>1</v>
@@ -6259,7 +6271,7 @@
         <v>1</v>
       </c>
       <c r="T45" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.0625</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -6274,16 +6286,16 @@
         <v>5</v>
       </c>
       <c r="Y45" t="n">
-        <v>35.97439230769231</v>
+        <v>35.5417</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>3|5|24|38|48|49|44</t>
+          <t>8|14|23|29|38|49|36</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -6321,25 +6333,25 @@
         <v>6</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I46" t="n">
         <v>9</v>
       </c>
       <c r="J46" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K46" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L46" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M46" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="N46" t="n">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -6348,7 +6360,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -6376,16 +6388,16 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>3|9|14|26|40|41|24</t>
+          <t>2|9|24|31|41|44|33</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47">
@@ -6416,28 +6428,28 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J47" t="n">
         <v>24</v>
       </c>
       <c r="K47" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="L47" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M47" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="N47" t="n">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -6446,7 +6458,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -6455,7 +6467,7 @@
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>0.0625</v>
+        <v>0.05882352941176471</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -6470,20 +6482,20 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>35.5417</v>
+        <v>35.43140588235294</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>2|13|24|37|38|49|33</t>
+          <t>3|6|24|31|34|43|10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48">
@@ -6517,25 +6529,25 @@
         <v>7</v>
       </c>
       <c r="H48" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J48" t="n">
         <v>24</v>
       </c>
       <c r="K48" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L48" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M48" t="n">
         <v>48</v>
       </c>
       <c r="N48" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -6544,7 +6556,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -6572,16 +6584,16 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>6|19|24|31|40|47|48</t>
+          <t>3|13|24|26|32|41|48</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="49">
@@ -6612,38 +6624,38 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J49" t="n">
         <v>24</v>
       </c>
       <c r="K49" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L49" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="M49" t="n">
+        <v>26</v>
+      </c>
+      <c r="N49" t="n">
+        <v>139</v>
+      </c>
+      <c r="O49" t="n">
+        <v>3</v>
+      </c>
+      <c r="P49" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q49" t="n">
         <v>42</v>
       </c>
-      <c r="N49" t="n">
-        <v>159</v>
-      </c>
-      <c r="O49" t="n">
-        <v>3</v>
-      </c>
-      <c r="P49" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>47</v>
-      </c>
       <c r="R49" t="n">
         <v>1</v>
       </c>
@@ -6651,7 +6663,7 @@
         <v>1</v>
       </c>
       <c r="T49" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.05555555555555555</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -6666,20 +6678,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.43140588235294</v>
+        <v>35.33336666666666</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>2|3|24|33|48|49|42</t>
+          <t>3|4|24|29|34|45|26</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50">
@@ -6713,25 +6725,25 @@
         <v>8</v>
       </c>
       <c r="H50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J50" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K50" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L50" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M50" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="N50" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -6740,7 +6752,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -6768,16 +6780,16 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>2|11|13|26|39|40|7</t>
+          <t>1|5|9|30|38|44|27</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51">
@@ -6814,31 +6826,31 @@
         <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J51" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K51" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L51" t="n">
+        <v>32</v>
+      </c>
+      <c r="M51" t="n">
+        <v>46</v>
+      </c>
+      <c r="N51" t="n">
+        <v>133</v>
+      </c>
+      <c r="O51" t="n">
+        <v>3</v>
+      </c>
+      <c r="P51" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q51" t="n">
         <v>42</v>
-      </c>
-      <c r="M51" t="n">
-        <v>18</v>
-      </c>
-      <c r="N51" t="n">
-        <v>155</v>
-      </c>
-      <c r="O51" t="n">
-        <v>3</v>
-      </c>
-      <c r="P51" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>46</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -6866,16 +6878,16 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|8|15|38|42|49|18</t>
+          <t>3|4|20|29|32|45|46</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52">
@@ -6909,34 +6921,34 @@
         <v>9</v>
       </c>
       <c r="H52" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I52" t="n">
+        <v>11</v>
+      </c>
+      <c r="J52" t="n">
         <v>13</v>
-      </c>
-      <c r="J52" t="n">
-        <v>20</v>
       </c>
       <c r="K52" t="n">
         <v>26</v>
       </c>
       <c r="L52" t="n">
+        <v>39</v>
+      </c>
+      <c r="M52" t="n">
+        <v>7</v>
+      </c>
+      <c r="N52" t="n">
+        <v>131</v>
+      </c>
+      <c r="O52" t="n">
+        <v>3</v>
+      </c>
+      <c r="P52" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q52" t="n">
         <v>38</v>
-      </c>
-      <c r="M52" t="n">
-        <v>35</v>
-      </c>
-      <c r="N52" t="n">
-        <v>143</v>
-      </c>
-      <c r="O52" t="n">
-        <v>3</v>
-      </c>
-      <c r="P52" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>36</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -6964,16 +6976,16 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>5|13|20|26|38|41|35</t>
+          <t>2|11|13|26|39|40|7</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53">
@@ -7007,34 +7019,34 @@
         <v>19</v>
       </c>
       <c r="H53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I53" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J53" t="n">
         <v>20</v>
       </c>
       <c r="K53" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L53" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M53" t="n">
+        <v>34</v>
+      </c>
+      <c r="N53" t="n">
+        <v>157</v>
+      </c>
+      <c r="O53" t="n">
+        <v>3</v>
+      </c>
+      <c r="P53" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q53" t="n">
         <v>47</v>
-      </c>
-      <c r="N53" t="n">
-        <v>155</v>
-      </c>
-      <c r="O53" t="n">
-        <v>3</v>
-      </c>
-      <c r="P53" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>46</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -7062,12 +7074,12 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|12|20|33|38|49|47</t>
+          <t>2|13|20|29|44|49|34</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -7105,25 +7117,25 @@
         <v>10</v>
       </c>
       <c r="H54" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J54" t="n">
         <v>24</v>
       </c>
       <c r="K54" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L54" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="M54" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N54" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -7132,7 +7144,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -7160,16 +7172,16 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>5|8|24|30|39|41|16</t>
+          <t>2|16|24|29|31|43|18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55">
@@ -7206,10 +7218,10 @@
         <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J55" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K55" t="n">
         <v>38</v>
@@ -7218,10 +7230,10 @@
         <v>42</v>
       </c>
       <c r="M55" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="N55" t="n">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -7258,12 +7270,12 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|4|5|38|42|49|6</t>
+          <t>3|8|15|38|42|49|17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB55" t="n">
@@ -7347,10 +7359,10 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
@@ -7361,24 +7373,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H3" t="n">
         <v>0.16</v>
@@ -7438,10 +7450,10 @@
         <v>2.6667</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5333</v>
+        <v>0.6667</v>
       </c>
     </row>
   </sheetData>
@@ -7478,7 +7490,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12703</t>
+          <t>12709</t>
         </is>
       </c>
     </row>
@@ -7526,7 +7538,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-23 00:00:00</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7562,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-23 08:14:23</t>
+          <t>2026-05-24 05:27:04</t>
         </is>
       </c>
     </row>
@@ -7624,7 +7636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1 model/game combinations are currently beating Random_Baseline.</t>
+          <t>0 model/game combinations are currently beating Random_Baseline.</t>
         </is>
       </c>
     </row>
@@ -7772,16 +7784,16 @@
         <v>15</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7583</v>
+        <v>0.7483</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.775</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
         <v>2.6667</v>
@@ -7793,13 +7805,13 @@
         <v>15</v>
       </c>
       <c r="N2" t="n">
+        <v>9</v>
+      </c>
+      <c r="O2" t="n">
         <v>10</v>
       </c>
-      <c r="O2" t="n">
-        <v>8</v>
-      </c>
       <c r="P2" t="n">
-        <v>0.5333</v>
+        <v>0.6667</v>
       </c>
     </row>
     <row r="3">
@@ -7826,22 +7838,22 @@
         <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7833</v>
+        <v>0.8133</v>
       </c>
       <c r="H3" t="n">
-        <v>0.795</v>
+        <v>0.82</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
         <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>2.7333</v>
+        <v>2.6</v>
       </c>
       <c r="L3" t="n">
-        <v>2.5333</v>
+        <v>2.6</v>
       </c>
       <c r="M3" t="n">
         <v>15</v>
@@ -7850,10 +7862,10 @@
         <v>8</v>
       </c>
       <c r="O3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4667</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="4">
@@ -7870,7 +7882,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -7880,28 +7892,28 @@
         <v>15</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6617</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>0.67</v>
+        <v>0.6133</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3333</v>
+        <v>2.2</v>
       </c>
       <c r="L4" t="n">
-        <v>2.3333</v>
+        <v>2.2</v>
       </c>
       <c r="M4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
         <v>4</v>
@@ -7924,7 +7936,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_Recent50</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -7934,34 +7946,34 @@
         <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6367</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6467000000000001</v>
+        <v>0.6483</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="L5" t="n">
-        <v>2.3333</v>
+        <v>2.2</v>
       </c>
       <c r="M5" t="n">
         <v>14</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2667</v>
+        <v>0.0667</v>
       </c>
     </row>
     <row r="6">
@@ -7978,7 +7990,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -7988,25 +8000,25 @@
         <v>15</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6833</v>
+        <v>0.6783</v>
       </c>
       <c r="H6" t="n">
-        <v>0.695</v>
+        <v>0.6883</v>
       </c>
       <c r="I6" t="n">
         <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>2.3333</v>
+        <v>2.1333</v>
       </c>
       <c r="L6" t="n">
-        <v>2.2667</v>
+        <v>2.1333</v>
       </c>
       <c r="M6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N6" t="n">
         <v>5</v>
@@ -8032,7 +8044,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Weighted_Recent50</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -8042,28 +8054,28 @@
         <v>15</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6417</v>
+        <v>0.65</v>
       </c>
       <c r="H7" t="n">
-        <v>0.655</v>
+        <v>0.6633</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>2.2667</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>2.2667</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
         <v>14</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>5</v>
@@ -8096,10 +8108,10 @@
         <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>0.673</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.673</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="I8" t="n">
         <v>3</v>
@@ -8108,16 +8120,16 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="L8" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="M8" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="N8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -8128,15 +8140,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -8146,10 +8158,10 @@
         <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>0.721</v>
+        <v>0.671</v>
       </c>
       <c r="H9" t="n">
-        <v>0.721</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="I9" t="n">
         <v>3</v>
@@ -8158,19 +8170,23 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="L9" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="M9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="N9" t="n">
-        <v>15</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="O9" t="n">
+        <v>16</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -8182,7 +8198,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -8196,34 +8212,34 @@
         <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>0.62</v>
+        <v>0.596</v>
       </c>
       <c r="H10" t="n">
-        <v>0.636</v>
+        <v>0.612</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="M10" t="n">
         <v>64</v>
       </c>
       <c r="N10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P10" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="11">
@@ -8232,7 +8248,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -8240,7 +8256,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -8250,10 +8266,10 @@
         <v>100</v>
       </c>
       <c r="G11" t="n">
-        <v>0.707</v>
+        <v>0.658</v>
       </c>
       <c r="H11" t="n">
-        <v>0.707</v>
+        <v>0.676</v>
       </c>
       <c r="I11" t="n">
         <v>4</v>
@@ -8262,19 +8278,23 @@
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="L11" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="M11" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="O11" t="n">
+        <v>15</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -8282,7 +8302,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -8290,7 +8310,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -8300,35 +8320,31 @@
         <v>100</v>
       </c>
       <c r="G12" t="n">
-        <v>0.596</v>
+        <v>0.68</v>
       </c>
       <c r="H12" t="n">
-        <v>0.611</v>
+        <v>0.68</v>
       </c>
       <c r="I12" t="n">
         <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="L12" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="M12" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="N12" t="n">
-        <v>8</v>
-      </c>
-      <c r="O12" t="n">
-        <v>14</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.14</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -8340,11 +8356,11 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -8354,16 +8370,16 @@
         <v>100</v>
       </c>
       <c r="G13" t="n">
-        <v>0.695</v>
+        <v>0.677</v>
       </c>
       <c r="H13" t="n">
-        <v>0.695</v>
+        <v>0.677</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
         <v>1.69</v>
@@ -8372,10 +8388,10 @@
         <v>1.69</v>
       </c>
       <c r="M13" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -8386,11 +8402,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -8404,31 +8420,35 @@
         <v>100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.668</v>
+        <v>0.6</v>
       </c>
       <c r="H14" t="n">
-        <v>0.668</v>
+        <v>0.612</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="L14" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="M14" t="n">
         <v>59</v>
       </c>
       <c r="N14" t="n">
-        <v>9</v>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="O14" t="n">
+        <v>8</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -8436,15 +8456,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -8454,10 +8474,10 @@
         <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>0.598</v>
+        <v>0.675</v>
       </c>
       <c r="H15" t="n">
-        <v>0.611</v>
+        <v>0.675</v>
       </c>
       <c r="I15" t="n">
         <v>3</v>
@@ -8466,23 +8486,19 @@
         <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="L15" t="n">
         <v>1.67</v>
       </c>
       <c r="M15" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="N15" t="n">
-        <v>8</v>
-      </c>
-      <c r="O15" t="n">
-        <v>12</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0.12</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -8490,15 +8506,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -8508,10 +8524,10 @@
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.609</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>0.626</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
@@ -8520,23 +8536,19 @@
         <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="L16" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="M16" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="N16" t="n">
-        <v>6</v>
-      </c>
-      <c r="O16" t="n">
-        <v>13</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0.13</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -8552,7 +8564,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -8562,10 +8574,10 @@
         <v>100</v>
       </c>
       <c r="G17" t="n">
-        <v>0.605</v>
+        <v>0.616</v>
       </c>
       <c r="H17" t="n">
-        <v>0.628</v>
+        <v>0.632</v>
       </c>
       <c r="I17" t="n">
         <v>3</v>
@@ -8574,22 +8586,22 @@
         <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="L17" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="M17" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O17" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="P17" t="n">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="18">
@@ -8598,7 +8610,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -8606,7 +8618,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -8616,10 +8628,10 @@
         <v>100</v>
       </c>
       <c r="G18" t="n">
-        <v>0.662</v>
+        <v>0.6</v>
       </c>
       <c r="H18" t="n">
-        <v>0.662</v>
+        <v>0.614</v>
       </c>
       <c r="I18" t="n">
         <v>3</v>
@@ -8628,19 +8640,23 @@
         <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="L18" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="N18" t="n">
-        <v>9</v>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="O18" t="n">
+        <v>10</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -8648,7 +8664,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -8656,7 +8672,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -8666,10 +8682,10 @@
         <v>100</v>
       </c>
       <c r="G19" t="n">
-        <v>0.585</v>
+        <v>0.726</v>
       </c>
       <c r="H19" t="n">
-        <v>0.602</v>
+        <v>0.726</v>
       </c>
       <c r="I19" t="n">
         <v>3</v>
@@ -8678,23 +8694,19 @@
         <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="L19" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="M19" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N19" t="n">
-        <v>7</v>
-      </c>
-      <c r="O19" t="n">
-        <v>16</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0.16</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -9140,10 +9152,10 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>0.673</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.673</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>3</v>
@@ -9152,23 +9164,23 @@
         <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="L2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="M2" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="N2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -9180,7 +9192,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -9190,10 +9202,10 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>0.62</v>
+        <v>0.671</v>
       </c>
       <c r="H3" t="n">
-        <v>0.636</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="I3" t="n">
         <v>3</v>
@@ -9202,16 +9214,16 @@
         <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="L3" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="M3" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O3" t="n">
         <v>16</v>
@@ -9298,16 +9310,16 @@
         <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7583</v>
+        <v>0.7483</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.775</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
         <v>2.6667</v>
@@ -9319,13 +9331,13 @@
         <v>15</v>
       </c>
       <c r="N5" t="n">
+        <v>9</v>
+      </c>
+      <c r="O5" t="n">
         <v>10</v>
       </c>
-      <c r="O5" t="n">
-        <v>8</v>
-      </c>
       <c r="P5" t="n">
-        <v>0.5333</v>
+        <v>0.6667</v>
       </c>
     </row>
   </sheetData>
@@ -9391,10 +9403,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="D2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -9416,20 +9428,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="D3" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.08</v>
+        <v>-0.15</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -9445,20 +9457,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="D4" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="E4" t="n">
         <v>-0.15</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -9478,16 +9490,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="D5" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="E5" t="n">
         <v>-0.17</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -9503,20 +9515,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1.67</v>
       </c>
       <c r="D6" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.19</v>
+        <v>-0.17</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -9532,20 +9544,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="D7" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.26</v>
+        <v>-0.22</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -9561,24 +9573,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="D8" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9590,20 +9602,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="D9" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -9619,17 +9631,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="D10" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -9652,16 +9664,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="D11" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.06</v>
+        <v>-0.12</v>
       </c>
       <c r="F11" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -9677,20 +9689,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="D12" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.15</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -9706,20 +9718,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="D13" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.12</v>
+        <v>-0.16</v>
       </c>
       <c r="F13" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -9942,16 +9954,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.5333</v>
+        <v>2.6</v>
       </c>
       <c r="D21" t="n">
         <v>2.6667</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1334</v>
+        <v>-0.0667</v>
       </c>
       <c r="F21" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -9967,20 +9979,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.3333</v>
+        <v>2.2</v>
       </c>
       <c r="D22" t="n">
         <v>2.6667</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3334</v>
+        <v>-0.4667</v>
       </c>
       <c r="F22" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -9996,20 +10008,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_Recent50</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2.3333</v>
+        <v>2.2</v>
       </c>
       <c r="D23" t="n">
         <v>2.6667</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3334</v>
+        <v>-0.4667</v>
       </c>
       <c r="F23" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -10025,20 +10037,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.2667</v>
+        <v>2.1333</v>
       </c>
       <c r="D24" t="n">
         <v>2.6667</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4</v>
+        <v>-0.5334</v>
       </c>
       <c r="F24" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -10054,20 +10066,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Weighted_Recent50</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.2667</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
         <v>2.6667</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.4</v>
+        <v>-0.6667</v>
       </c>
       <c r="F25" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>

--- a/data/exports/reporting/daily_lottery_summary.xlsx
+++ b/data/exports/reporting/daily_lottery_summary.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:17</t>
+          <t>2026-05-25 14:34:32</t>
         </is>
       </c>
     </row>
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12709</v>
+        <v>12713</v>
       </c>
     </row>
     <row r="4">
@@ -480,7 +480,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
     </row>
@@ -654,24 +654,24 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I2" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="K2" t="n">
         <v>31</v>
@@ -679,7 +679,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>364517.7</v>
+        <v>300000</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -691,57 +691,51 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lotto Plus 2</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plus 2</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J3" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K3" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M3" t="n">
-        <v>19</v>
-      </c>
-      <c r="N3" t="n">
-        <v>8500000</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -751,12 +745,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -774,34 +768,26 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="I4" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="J4" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="K4" t="n">
-        <v>49</v>
-      </c>
-      <c r="L4" t="n">
-        <v>53</v>
-      </c>
-      <c r="M4" t="n">
-        <v>34</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>10500000</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>364517.7</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -811,17 +797,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lotto Plus 1</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plus 1</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -834,34 +820,28 @@
         </is>
       </c>
       <c r="G5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H5" t="n">
+        <v>24</v>
+      </c>
+      <c r="I5" t="n">
+        <v>40</v>
+      </c>
+      <c r="J5" t="n">
+        <v>41</v>
+      </c>
+      <c r="K5" t="n">
+        <v>46</v>
+      </c>
+      <c r="L5" t="n">
+        <v>47</v>
+      </c>
+      <c r="M5" t="n">
         <v>9</v>
       </c>
-      <c r="H5" t="n">
-        <v>16</v>
-      </c>
-      <c r="I5" t="n">
-        <v>22</v>
-      </c>
-      <c r="J5" t="n">
-        <v>27</v>
-      </c>
-      <c r="K5" t="n">
-        <v>30</v>
-      </c>
-      <c r="L5" t="n">
-        <v>41</v>
-      </c>
-      <c r="M5" t="n">
-        <v>52</v>
-      </c>
-      <c r="N5" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -876,43 +856,43 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="I6" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="J6" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K6" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L6" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -925,51 +905,57 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="J7" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="K7" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="L7" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="M7" t="n">
-        <v>9</v>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="N7" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -979,49 +965,57 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto Plus 2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
         <v>23</v>
       </c>
       <c r="J8" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K8" t="n">
-        <v>36</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+        <v>33</v>
+      </c>
+      <c r="L8" t="n">
+        <v>47</v>
+      </c>
+      <c r="M8" t="n">
+        <v>19</v>
+      </c>
       <c r="N8" t="n">
-        <v>474917.1</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
+        <v>8500000</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1031,49 +1025,51 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PowerBall Plus</t>
+          <t>Lotto Plus 1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Plus 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I9" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J9" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K9" t="n">
-        <v>48</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="L9" t="n">
+        <v>41</v>
+      </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="N9" t="n">
-        <v>96000000</v>
+        <v>6000000</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1089,12 +1085,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1112,32 +1108,26 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I10" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="n">
-        <v>18</v>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>474917.1</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1147,12 +1137,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1162,34 +1152,40 @@
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J11" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K11" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>18</v>
+      </c>
       <c r="N11" t="n">
-        <v>345741</v>
-      </c>
-      <c r="O11" t="inlineStr"/>
+        <v>100000000</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1199,51 +1195,55 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>PowerBall Plus</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I12" t="n">
+        <v>15</v>
+      </c>
+      <c r="J12" t="n">
+        <v>22</v>
+      </c>
+      <c r="K12" t="n">
+        <v>48</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
         <v>5</v>
       </c>
-      <c r="H12" t="n">
-        <v>7</v>
-      </c>
-      <c r="I12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J12" t="n">
-        <v>24</v>
-      </c>
-      <c r="K12" t="n">
-        <v>43</v>
-      </c>
-      <c r="L12" t="n">
-        <v>48</v>
-      </c>
-      <c r="M12" t="n">
-        <v>22</v>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>96000000</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1258,43 +1258,43 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J13" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K13" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L13" t="n">
         <v>46</v>
       </c>
       <c r="M13" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1307,48 +1307,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J14" t="n">
+        <v>12</v>
+      </c>
+      <c r="K14" t="n">
         <v>20</v>
       </c>
-      <c r="K14" t="n">
-        <v>21</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="n">
-        <v>340306.8</v>
-      </c>
+      <c r="L14" t="n">
+        <v>46</v>
+      </c>
+      <c r="M14" t="n">
+        <v>9</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1359,12 +1361,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1374,42 +1376,34 @@
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J15" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="K15" t="n">
-        <v>24</v>
-      </c>
-      <c r="L15" t="n">
-        <v>58</v>
-      </c>
-      <c r="M15" t="n">
-        <v>53</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>8500000</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>345741</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1419,57 +1413,51 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lotto Plus 1</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plus 1</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="I16" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="K16" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="L16" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="M16" t="n">
-        <v>41</v>
-      </c>
-      <c r="N16" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1479,57 +1467,51 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lotto Plus 2</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Plus 2</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H17" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I17" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J17" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K17" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="L17" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="M17" t="n">
-        <v>28</v>
-      </c>
-      <c r="N17" t="n">
-        <v>7500000</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1544,12 +1526,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1562,25 +1544,25 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H18" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K18" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L18" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="M18" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -1598,12 +1580,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1616,25 +1598,25 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H19" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J19" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K19" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L19" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="M19" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -1647,51 +1629,57 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>Lotto Plus 2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Plus 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I20" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K20" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L20" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="M20" t="n">
-        <v>18</v>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="N20" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1701,51 +1689,57 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="J21" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="K21" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="L21" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="M21" t="n">
-        <v>15</v>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+        <v>53</v>
+      </c>
+      <c r="N21" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1755,55 +1749,49 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PowerBall Plus</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
+        <v>6</v>
+      </c>
+      <c r="I22" t="n">
+        <v>14</v>
+      </c>
+      <c r="J22" t="n">
+        <v>20</v>
+      </c>
+      <c r="K22" t="n">
         <v>21</v>
       </c>
-      <c r="I22" t="n">
-        <v>23</v>
-      </c>
-      <c r="J22" t="n">
-        <v>41</v>
-      </c>
-      <c r="K22" t="n">
-        <v>43</v>
-      </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="n">
-        <v>11</v>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
-        <v>93000000</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>340306.8</v>
+      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1813,49 +1801,51 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto Plus 1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H23" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="I23" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="J23" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="K23" t="n">
-        <v>48</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="L23" t="n">
+        <v>55</v>
+      </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="N23" t="n">
-        <v>91000000</v>
+        <v>5000000</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -1923,12 +1913,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1938,34 +1928,40 @@
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H25" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J25" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="K25" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>4</v>
+      </c>
       <c r="N25" t="n">
-        <v>300000</v>
-      </c>
-      <c r="O25" t="inlineStr"/>
+        <v>91000000</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1975,51 +1971,55 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>PowerBall Plus</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H26" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I26" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="K26" t="n">
-        <v>26</v>
-      </c>
-      <c r="L26" t="n">
-        <v>33</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
-        <v>37</v>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="N26" t="n">
+        <v>93000000</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2258,7 +2258,7 @@
         <v>8</v>
       </c>
       <c r="Y2" t="n">
-        <v>73.84</v>
+        <v>73.94</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -2299,7 +2299,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
         <v>10</v>
@@ -2311,20 +2311,20 @@
         <v>25</v>
       </c>
       <c r="L3" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="O3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P3" t="n">
         <v>2</v>
       </c>
-      <c r="P3" t="n">
-        <v>3</v>
-      </c>
       <c r="Q3" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -2348,16 +2348,16 @@
         <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>47.84</v>
+        <v>47.94</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6|10|12|25|27</t>
+          <t>5|10|12|25|33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -2389,23 +2389,23 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K4" t="n">
+        <v>21</v>
+      </c>
+      <c r="L4" t="n">
         <v>25</v>
-      </c>
-      <c r="L4" t="n">
-        <v>35</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -2414,7 +2414,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -2438,16 +2438,16 @@
         <v>5</v>
       </c>
       <c r="Y4" t="n">
-        <v>42.84</v>
+        <v>42.94</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3|10|14|25|35</t>
+          <t>10|12|15|21|25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -2479,23 +2479,23 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -2504,7 +2504,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -2528,16 +2528,16 @@
         <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>40.34</v>
+        <v>40.44</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10|12|15|21|25</t>
+          <t>5|6|9|22|27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -2569,32 +2569,32 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K6" t="n">
         <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O6" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" t="n">
-        <v>3</v>
-      </c>
       <c r="Q6" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -2618,16 +2618,16 @@
         <v>5</v>
       </c>
       <c r="Y6" t="n">
-        <v>38.84</v>
+        <v>38.94</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4|6|10|25|35</t>
+          <t>5|8|14|25|27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -2659,23 +2659,23 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -2684,7 +2684,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -2708,16 +2708,16 @@
         <v>5</v>
       </c>
       <c r="Y7" t="n">
-        <v>37.84</v>
+        <v>37.94</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5|10|12|23|27</t>
+          <t>2|10|11|25|35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -2749,23 +2749,23 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K8" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L8" t="n">
         <v>27</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="O8" t="n">
         <v>3</v>
@@ -2774,7 +2774,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -2798,16 +2798,16 @@
         <v>5</v>
       </c>
       <c r="Y8" t="n">
-        <v>37.12571428571429</v>
+        <v>37.22571428571428</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3|8|10|25|27</t>
+          <t>6|10|15|23|27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -2839,23 +2839,23 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
+        <v>8</v>
+      </c>
+      <c r="J9" t="n">
         <v>10</v>
-      </c>
-      <c r="J9" t="n">
-        <v>14</v>
       </c>
       <c r="K9" t="n">
         <v>25</v>
       </c>
       <c r="L9" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -2864,7 +2864,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -2888,16 +2888,16 @@
         <v>5</v>
       </c>
       <c r="Y9" t="n">
-        <v>36.59</v>
+        <v>36.69</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9|10|14|25|31</t>
+          <t>3|8|10|25|27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -2929,23 +2929,23 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K10" t="n">
         <v>25</v>
       </c>
       <c r="L10" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -2954,7 +2954,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -2978,16 +2978,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>36.17333333333333</v>
+        <v>36.27333333333333</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4|6|9|25|27</t>
+          <t>9|10|14|25|31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -3022,20 +3022,20 @@
         <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="K11" t="n">
         <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -3044,7 +3044,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -3068,16 +3068,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>35.84</v>
+        <v>35.94</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4|14|17|25|35</t>
+          <t>4|6|9|25|27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -3118,14 +3118,14 @@
         <v>14</v>
       </c>
       <c r="K12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L12" t="n">
         <v>25</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O12" t="n">
         <v>2</v>
@@ -3158,16 +3158,16 @@
         <v>5</v>
       </c>
       <c r="Y12" t="n">
-        <v>35.56727272727272</v>
+        <v>35.66727272727273</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4|10|14|23|25</t>
+          <t>4|10|14|21|25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr"/>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB23" t="n">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -5172,7 +5172,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -5208,16 +5208,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.66670000000001</v>
+        <v>74.4375</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|2</t>
+          <t>1|3|5|44|46|49|31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -5270,7 +5270,7 @@
         <v>46</v>
       </c>
       <c r="M35" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="N35" t="n">
         <v>148</v>
@@ -5306,16 +5306,16 @@
         <v>8</v>
       </c>
       <c r="Y35" t="n">
-        <v>74.66670000000001</v>
+        <v>74.4375</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|2</t>
+          <t>1|3|5|44|46|49|31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB35" t="n">
@@ -5353,25 +5353,25 @@
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J36" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K36" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L36" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M36" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="N36" t="n">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -5380,7 +5380,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -5404,20 +5404,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>48.6667</v>
+        <v>48.4375</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17|19|20|31|38|44|15</t>
+          <t>1|9|24|30|44|45|4</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37">
@@ -5448,25 +5448,25 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J37" t="n">
         <v>24</v>
       </c>
       <c r="K37" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L37" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="M37" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="N37" t="n">
         <v>151</v>
@@ -5478,7 +5478,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -5487,7 +5487,7 @@
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -5499,23 +5499,23 @@
         <v>0.5</v>
       </c>
       <c r="X37" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>38.80955714285714</v>
+        <v>35.9375</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>1|2|24|33|42|49|23</t>
+          <t>3|5|24|37|38|44|20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38">
@@ -5549,25 +5549,25 @@
         <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I38" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K38" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L38" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M38" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="N38" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -5576,7 +5576,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -5600,20 +5600,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>43.6667</v>
+        <v>43.4375</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>5|13|24|30|41|48|47</t>
+          <t>9|16|22|31|44|45|7</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39">
@@ -5644,28 +5644,28 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H39" t="n">
         <v>3</v>
       </c>
       <c r="I39" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J39" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="K39" t="n">
+        <v>25</v>
+      </c>
+      <c r="L39" t="n">
         <v>38</v>
       </c>
-      <c r="L39" t="n">
-        <v>44</v>
-      </c>
       <c r="M39" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="N39" t="n">
-        <v>165</v>
+        <v>121</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -5674,7 +5674,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -5683,7 +5683,7 @@
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -5698,20 +5698,20 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>36.1667</v>
+        <v>35.74519230769231</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>3|8|23|38|44|49|39</t>
+          <t>3|4|12|25|38|39|15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40">
@@ -5745,34 +5745,34 @@
         <v>3</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I40" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J40" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K40" t="n">
+        <v>26</v>
+      </c>
+      <c r="L40" t="n">
+        <v>38</v>
+      </c>
+      <c r="M40" t="n">
+        <v>35</v>
+      </c>
+      <c r="N40" t="n">
+        <v>141</v>
+      </c>
+      <c r="O40" t="n">
+        <v>3</v>
+      </c>
+      <c r="P40" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q40" t="n">
         <v>31</v>
-      </c>
-      <c r="L40" t="n">
-        <v>40</v>
-      </c>
-      <c r="M40" t="n">
-        <v>30</v>
-      </c>
-      <c r="N40" t="n">
-        <v>157</v>
-      </c>
-      <c r="O40" t="n">
-        <v>3</v>
-      </c>
-      <c r="P40" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>43</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -5796,20 +5796,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>41.1667</v>
+        <v>40.9375</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>2|19|20|31|40|45|30</t>
+          <t>9|11|17|26|38|40|35</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41">
@@ -5840,28 +5840,28 @@
         </is>
       </c>
       <c r="G41" t="n">
+        <v>13</v>
+      </c>
+      <c r="H41" t="n">
+        <v>3</v>
+      </c>
+      <c r="I41" t="n">
+        <v>9</v>
+      </c>
+      <c r="J41" t="n">
         <v>12</v>
       </c>
-      <c r="H41" t="n">
-        <v>6</v>
-      </c>
-      <c r="I41" t="n">
-        <v>11</v>
-      </c>
-      <c r="J41" t="n">
-        <v>20</v>
-      </c>
       <c r="K41" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="L41" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M41" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="N41" t="n">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -5870,7 +5870,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -5879,7 +5879,7 @@
         <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -5894,20 +5894,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>35.97439230769231</v>
+        <v>35.58035714285714</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>6|11|20|39|44|49|40</t>
+          <t>3|9|12|25|38|44|49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42">
@@ -5941,34 +5941,34 @@
         <v>4</v>
       </c>
       <c r="H42" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J42" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K42" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="L42" t="n">
+        <v>38</v>
+      </c>
+      <c r="M42" t="n">
+        <v>5</v>
+      </c>
+      <c r="N42" t="n">
+        <v>141</v>
+      </c>
+      <c r="O42" t="n">
+        <v>3</v>
+      </c>
+      <c r="P42" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q42" t="n">
         <v>44</v>
-      </c>
-      <c r="M42" t="n">
-        <v>37</v>
-      </c>
-      <c r="N42" t="n">
-        <v>163</v>
-      </c>
-      <c r="O42" t="n">
-        <v>3</v>
-      </c>
-      <c r="P42" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>36</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -5992,16 +5992,16 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>39.6667</v>
+        <v>39.4375</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>9|11|14|40|44|45|37</t>
+          <t>1|7|24|26|38|45|5</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB42" t="n">
@@ -6042,22 +6042,22 @@
         <v>3</v>
       </c>
       <c r="I43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J43" t="n">
         <v>24</v>
       </c>
       <c r="K43" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="L43" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M43" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="N43" t="n">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -6066,7 +6066,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -6090,20 +6090,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>35.6667</v>
+        <v>35.4375</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>3|5|24|37|38|44|19</t>
+          <t>3|4|24|29|34|45|27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44">
@@ -6137,22 +6137,22 @@
         <v>5</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I44" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J44" t="n">
         <v>24</v>
       </c>
       <c r="K44" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="L44" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M44" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="N44" t="n">
         <v>163</v>
@@ -6164,7 +6164,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -6188,20 +6188,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>38.6667</v>
+        <v>38.4375</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>2|9|24|40|43|45|34</t>
+          <t>6|16|24|33|41|43|2</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45">
@@ -6235,25 +6235,25 @@
         <v>15</v>
       </c>
       <c r="H45" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I45" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J45" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K45" t="n">
         <v>29</v>
       </c>
       <c r="L45" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M45" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="N45" t="n">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="O45" t="n">
         <v>3</v>
@@ -6262,7 +6262,7 @@
         <v>3</v>
       </c>
       <c r="Q45" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R45" t="n">
         <v>1</v>
@@ -6286,20 +6286,20 @@
         <v>5</v>
       </c>
       <c r="Y45" t="n">
-        <v>35.5417</v>
+        <v>35.3125</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>8|14|23|29|38|49|36</t>
+          <t>3|4|20|29|42|45|18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB45" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46">
@@ -6336,22 +6336,22 @@
         <v>2</v>
       </c>
       <c r="I46" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J46" t="n">
         <v>24</v>
       </c>
       <c r="K46" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="L46" t="n">
         <v>41</v>
       </c>
       <c r="M46" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="N46" t="n">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -6360,7 +6360,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -6384,20 +6384,20 @@
         <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>37.95241428571428</v>
+        <v>37.72321428571428</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>2|9|24|31|41|44|33</t>
+          <t>2|19|24|39|41|42|7</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47">
@@ -6431,7 +6431,7 @@
         <v>16</v>
       </c>
       <c r="H47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I47" t="n">
         <v>6</v>
@@ -6440,16 +6440,16 @@
         <v>24</v>
       </c>
       <c r="K47" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L47" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="M47" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N47" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -6482,20 +6482,20 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>35.43140588235294</v>
+        <v>35.20220588235294</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|6|24|31|34|43|10</t>
+          <t>5|6|24|34|39|45|13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48">
@@ -6529,25 +6529,25 @@
         <v>7</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J48" t="n">
         <v>24</v>
       </c>
       <c r="K48" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="L48" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="M48" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="N48" t="n">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -6556,7 +6556,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -6580,20 +6580,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>37.4167</v>
+        <v>37.1875</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3|13|24|26|32|41|48</t>
+          <t>1|19|24|38|40|45|42</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49">
@@ -6627,25 +6627,25 @@
         <v>17</v>
       </c>
       <c r="H49" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I49" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K49" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L49" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M49" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="N49" t="n">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -6654,7 +6654,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -6678,20 +6678,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.33336666666666</v>
+        <v>35.10416666666666</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|4|24|29|34|45|26</t>
+          <t>9|17|20|31|42|46|10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50">
@@ -6725,25 +6725,25 @@
         <v>8</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I50" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J50" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K50" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L50" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="M50" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="N50" t="n">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -6752,7 +6752,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -6776,20 +6776,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>37.00003333333333</v>
+        <v>36.77083333333333</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>1|5|9|30|38|44|27</t>
+          <t>5|9|14|40|48|49|13</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51">
@@ -6826,22 +6826,22 @@
         <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J51" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K51" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L51" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M51" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="N51" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -6850,7 +6850,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -6874,20 +6874,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.24564736842105</v>
+        <v>35.01644736842105</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|4|20|29|32|45|46</t>
+          <t>3|6|24|31|34|43|11</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52">
@@ -6921,25 +6921,25 @@
         <v>9</v>
       </c>
       <c r="H52" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I52" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J52" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K52" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L52" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M52" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N52" t="n">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -6948,7 +6948,7 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -6972,20 +6972,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>36.6667</v>
+        <v>36.4375</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>2|11|13|26|39|40|7</t>
+          <t>5|9|22|30|40|45|1</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53">
@@ -7019,25 +7019,25 @@
         <v>19</v>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J53" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K53" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="L53" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M53" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="N53" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -7046,7 +7046,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -7070,16 +7070,16 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.1667</v>
+        <v>34.9375</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>2|13|20|29|44|49|34</t>
+          <t>3|6|15|40|42|49|46</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -7117,25 +7117,25 @@
         <v>10</v>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I54" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K54" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L54" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="M54" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="N54" t="n">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -7144,7 +7144,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -7168,20 +7168,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>36.39397272727273</v>
+        <v>36.16477272727273</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>2|16|24|29|31|43|18</t>
+          <t>6|18|19|31|39|44|48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="55">
@@ -7218,22 +7218,22 @@
         <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J55" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K55" t="n">
+        <v>34</v>
+      </c>
+      <c r="L55" t="n">
         <v>38</v>
       </c>
-      <c r="L55" t="n">
-        <v>42</v>
-      </c>
       <c r="M55" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="N55" t="n">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -7242,7 +7242,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -7266,20 +7266,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>35.09527142857143</v>
+        <v>34.86607142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|8|15|38|42|49|17</t>
+          <t>3|5|20|34|38|39|4</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -7359,10 +7359,10 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="G2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
@@ -7440,20 +7440,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6667</v>
+        <v>2.4375</v>
       </c>
       <c r="G5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6667</v>
+        <v>0.3125</v>
       </c>
     </row>
   </sheetData>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12709</t>
+          <t>12713</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-23 00:00:00</t>
+          <t>2026-05-24 00:00:00</t>
         </is>
       </c>
     </row>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:04</t>
+          <t>2026-05-25 14:23:59</t>
         </is>
       </c>
     </row>
@@ -7612,7 +7612,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UK49s: Random_Baseline is currently ranked first.</t>
+          <t>UK49s: Weighted_AllHistory_v1 is currently ranked first.</t>
         </is>
       </c>
     </row>
@@ -7636,7 +7636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0 model/game combinations are currently beating Random_Baseline.</t>
+          <t>1 model/game combinations are currently beating Random_Baseline.</t>
         </is>
       </c>
     </row>
@@ -7774,20 +7774,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>600</v>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7483</v>
+        <v>0.8217</v>
       </c>
       <c r="H2" t="n">
-        <v>0.775</v>
+        <v>0.8317</v>
       </c>
       <c r="I2" t="n">
         <v>4</v>
@@ -7796,22 +7796,22 @@
         <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>2.6667</v>
+        <v>2.5</v>
       </c>
       <c r="L2" t="n">
-        <v>2.6667</v>
+        <v>2.4375</v>
       </c>
       <c r="M2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6667</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="3">
@@ -7828,44 +7828,44 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>600</v>
       </c>
       <c r="F3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8133</v>
+        <v>0.7167</v>
       </c>
       <c r="H3" t="n">
-        <v>0.82</v>
+        <v>0.7267</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6</v>
+        <v>2.3125</v>
       </c>
       <c r="L3" t="n">
-        <v>2.6</v>
+        <v>2.3125</v>
       </c>
       <c r="M3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2667</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="4">
@@ -7889,13 +7889,13 @@
         <v>600</v>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6032999999999999</v>
+        <v>0.615</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6133</v>
+        <v>0.625</v>
       </c>
       <c r="I4" t="n">
         <v>3</v>
@@ -7904,22 +7904,22 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2</v>
+        <v>2.1875</v>
       </c>
       <c r="L4" t="n">
-        <v>2.2</v>
+        <v>2.1875</v>
       </c>
       <c r="M4" t="n">
         <v>13</v>
       </c>
       <c r="N4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O4" t="n">
         <v>5</v>
       </c>
-      <c r="O4" t="n">
-        <v>4</v>
-      </c>
       <c r="P4" t="n">
-        <v>0.2667</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="5">
@@ -7936,20 +7936,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Weighted_Recent50</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>600</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6467000000000001</v>
+        <v>0.6917</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6483</v>
+        <v>0.705</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
@@ -7958,10 +7958,10 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2</v>
+        <v>2.125</v>
       </c>
       <c r="L5" t="n">
-        <v>2.2</v>
+        <v>2.125</v>
       </c>
       <c r="M5" t="n">
         <v>14</v>
@@ -7970,10 +7970,10 @@
         <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0667</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="6">
@@ -7990,44 +7990,44 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>600</v>
       </c>
       <c r="F6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6483</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6633</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.0625</v>
+      </c>
+      <c r="M6" t="n">
         <v>15</v>
       </c>
-      <c r="G6" t="n">
-        <v>0.6783</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.6883</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2.1333</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2.1333</v>
-      </c>
-      <c r="M6" t="n">
-        <v>12</v>
-      </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2667</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="7">
@@ -8044,20 +8044,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_Recent50</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>600</v>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G7" t="n">
         <v>0.65</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6633</v>
+        <v>0.665</v>
       </c>
       <c r="I7" t="n">
         <v>3</v>
@@ -8072,16 +8072,16 @@
         <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
@@ -8108,10 +8108,10 @@
         <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.708</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.708</v>
       </c>
       <c r="I8" t="n">
         <v>3</v>
@@ -8120,16 +8120,16 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="L8" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="M8" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="N8" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -8248,15 +8248,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -8266,35 +8266,31 @@
         <v>100</v>
       </c>
       <c r="G11" t="n">
-        <v>0.658</v>
+        <v>0.742</v>
       </c>
       <c r="H11" t="n">
-        <v>0.676</v>
+        <v>0.742</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="L11" t="n">
         <v>1.76</v>
       </c>
       <c r="M11" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="N11" t="n">
-        <v>11</v>
-      </c>
-      <c r="O11" t="n">
-        <v>15</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.15</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -8302,15 +8298,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -8320,31 +8316,35 @@
         <v>100</v>
       </c>
       <c r="G12" t="n">
-        <v>0.68</v>
+        <v>0.658</v>
       </c>
       <c r="H12" t="n">
-        <v>0.68</v>
+        <v>0.676</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="L12" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="M12" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="N12" t="n">
+        <v>11</v>
+      </c>
+      <c r="O12" t="n">
         <v>15</v>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -8352,11 +8352,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -8370,19 +8370,19 @@
         <v>100</v>
       </c>
       <c r="G13" t="n">
-        <v>0.677</v>
+        <v>0.6</v>
       </c>
       <c r="H13" t="n">
-        <v>0.677</v>
+        <v>0.612</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="L13" t="n">
         <v>1.69</v>
@@ -8393,8 +8393,12 @@
       <c r="N13" t="n">
         <v>11</v>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+      <c r="O13" t="n">
+        <v>8</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -8406,11 +8410,11 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -8420,34 +8424,34 @@
         <v>100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6</v>
+        <v>0.616</v>
       </c>
       <c r="H14" t="n">
-        <v>0.612</v>
+        <v>0.632</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="L14" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="M14" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P14" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="15">
@@ -8460,7 +8464,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -8474,10 +8478,10 @@
         <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>0.675</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>0.675</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="I15" t="n">
         <v>3</v>
@@ -8486,16 +8490,16 @@
         <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="L15" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="M15" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -8510,7 +8514,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -8524,10 +8528,10 @@
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.674</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.674</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
@@ -8536,16 +8540,16 @@
         <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="L16" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="M16" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
@@ -8560,11 +8564,11 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -8574,10 +8578,10 @@
         <v>100</v>
       </c>
       <c r="G17" t="n">
-        <v>0.616</v>
+        <v>0.6</v>
       </c>
       <c r="H17" t="n">
-        <v>0.632</v>
+        <v>0.614</v>
       </c>
       <c r="I17" t="n">
         <v>3</v>
@@ -8586,22 +8590,22 @@
         <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="L17" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="M17" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N17" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P17" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="18">
@@ -8610,15 +8614,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -8628,10 +8632,10 @@
         <v>100</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6</v>
+        <v>0.704</v>
       </c>
       <c r="H18" t="n">
-        <v>0.614</v>
+        <v>0.704</v>
       </c>
       <c r="I18" t="n">
         <v>3</v>
@@ -8640,23 +8644,19 @@
         <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="M18" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N18" t="n">
-        <v>6</v>
-      </c>
-      <c r="O18" t="n">
-        <v>10</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0.1</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -8682,10 +8682,10 @@
         <v>100</v>
       </c>
       <c r="G19" t="n">
-        <v>0.726</v>
+        <v>0.698</v>
       </c>
       <c r="H19" t="n">
-        <v>0.726</v>
+        <v>0.698</v>
       </c>
       <c r="I19" t="n">
         <v>3</v>
@@ -8694,16 +8694,16 @@
         <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="L19" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="M19" t="n">
         <v>51</v>
       </c>
       <c r="N19" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -9152,10 +9152,10 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.708</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.708</v>
       </c>
       <c r="I2" t="n">
         <v>3</v>
@@ -9164,16 +9164,16 @@
         <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="L2" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="M2" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="N2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -9300,20 +9300,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>600</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7483</v>
+        <v>0.8217</v>
       </c>
       <c r="H5" t="n">
-        <v>0.775</v>
+        <v>0.8317</v>
       </c>
       <c r="I5" t="n">
         <v>4</v>
@@ -9322,22 +9322,22 @@
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>2.6667</v>
+        <v>2.5</v>
       </c>
       <c r="L5" t="n">
-        <v>2.6667</v>
+        <v>2.4375</v>
       </c>
       <c r="M5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6667</v>
+        <v>0.3125</v>
       </c>
     </row>
   </sheetData>
@@ -9403,10 +9403,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="D2" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -9428,20 +9428,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="D3" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.15</v>
+        <v>-0.18</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -9457,20 +9457,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="D4" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.15</v>
+        <v>-0.29</v>
       </c>
       <c r="F4" t="n">
-        <v>-2</v>
+        <v>-9</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -9486,20 +9486,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="D5" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.17</v>
+        <v>-0.29</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -9515,20 +9515,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="D6" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.17</v>
+        <v>-0.31</v>
       </c>
       <c r="F6" t="n">
-        <v>-2</v>
+        <v>-11</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -9544,20 +9544,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="D7" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.22</v>
+        <v>-0.36</v>
       </c>
       <c r="F7" t="n">
-        <v>-1</v>
+        <v>-10</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -9921,24 +9921,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.6667</v>
+        <v>2.4375</v>
       </c>
       <c r="D20" t="n">
-        <v>2.6667</v>
+        <v>2.3125</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -9950,20 +9950,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.6</v>
+        <v>2.3125</v>
       </c>
       <c r="D21" t="n">
-        <v>2.6667</v>
+        <v>2.3125</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0667</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -9983,16 +9983,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.2</v>
+        <v>2.1875</v>
       </c>
       <c r="D22" t="n">
-        <v>2.6667</v>
+        <v>2.3125</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4667</v>
+        <v>-0.125</v>
       </c>
       <c r="F22" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -10008,20 +10008,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Weighted_Recent50</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2.2</v>
+        <v>2.125</v>
       </c>
       <c r="D23" t="n">
-        <v>2.6667</v>
+        <v>2.3125</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4667</v>
+        <v>-0.1875</v>
       </c>
       <c r="F23" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -10037,20 +10037,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.1333</v>
+        <v>2.0625</v>
       </c>
       <c r="D24" t="n">
-        <v>2.6667</v>
+        <v>2.3125</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5334</v>
+        <v>-0.25</v>
       </c>
       <c r="F24" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -10066,20 +10066,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_Recent50</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>2.6667</v>
+        <v>2.3125</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.6667</v>
+        <v>-0.3125</v>
       </c>
       <c r="F25" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>

--- a/data/exports/reporting/daily_lottery_summary.xlsx
+++ b/data/exports/reporting/daily_lottery_summary.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:32</t>
+          <t>2026-05-26 14:23:49</t>
         </is>
       </c>
     </row>
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12713</v>
+        <v>12716</v>
       </c>
     </row>
     <row r="4">
@@ -480,7 +480,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
     </row>
@@ -654,32 +654,32 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K2" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>300000</v>
+        <v>359265</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -706,33 +706,33 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="n">
+        <v>14</v>
+      </c>
+      <c r="J3" t="n">
         <v>17</v>
       </c>
-      <c r="I3" t="n">
-        <v>24</v>
-      </c>
-      <c r="J3" t="n">
-        <v>36</v>
-      </c>
       <c r="K3" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="L3" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -760,24 +760,24 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
         <v>31</v>
@@ -785,7 +785,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>364517.7</v>
+        <v>300000</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -802,43 +802,43 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I5" t="n">
         <v>24</v>
       </c>
-      <c r="I5" t="n">
-        <v>40</v>
-      </c>
       <c r="J5" t="n">
+        <v>26</v>
+      </c>
+      <c r="K5" t="n">
+        <v>28</v>
+      </c>
+      <c r="L5" t="n">
+        <v>45</v>
+      </c>
+      <c r="M5" t="n">
         <v>41</v>
-      </c>
-      <c r="K5" t="n">
-        <v>46</v>
-      </c>
-      <c r="L5" t="n">
-        <v>47</v>
-      </c>
-      <c r="M5" t="n">
-        <v>9</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -856,43 +856,43 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>9</v>
       </c>
       <c r="H6" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I6" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J6" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K6" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L6" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="M6" t="n">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -905,12 +905,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -928,34 +928,26 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="I7" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="J7" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="K7" t="n">
-        <v>49</v>
-      </c>
-      <c r="L7" t="n">
-        <v>53</v>
-      </c>
-      <c r="M7" t="n">
-        <v>34</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>10500000</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>364517.7</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -970,12 +962,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lotto Plus 2</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Plus 2</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -988,28 +980,28 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="I8" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="J8" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="K8" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="L8" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="M8" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="N8" t="n">
-        <v>8500000</v>
+        <v>10500000</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1085,49 +1077,57 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto Plus 2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
         <v>23</v>
       </c>
       <c r="J10" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K10" t="n">
-        <v>36</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+        <v>33</v>
+      </c>
+      <c r="L10" t="n">
+        <v>47</v>
+      </c>
+      <c r="M10" t="n">
+        <v>19</v>
+      </c>
       <c r="N10" t="n">
-        <v>474917.1</v>
-      </c>
-      <c r="O10" t="inlineStr"/>
+        <v>8500000</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1137,55 +1137,51 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I11" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J11" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="K11" t="n">
-        <v>25</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="L11" t="n">
+        <v>47</v>
+      </c>
       <c r="M11" t="n">
-        <v>18</v>
-      </c>
-      <c r="N11" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1195,55 +1191,51 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PowerBall Plus</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H12" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="J12" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K12" t="n">
-        <v>48</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
+        <v>35</v>
+      </c>
+      <c r="L12" t="n">
+        <v>38</v>
+      </c>
       <c r="M12" t="n">
-        <v>5</v>
-      </c>
-      <c r="N12" t="n">
-        <v>96000000</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1376,32 +1368,32 @@
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I15" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K15" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>345741</v>
+        <v>474917.1</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -1413,51 +1405,55 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>PowerBall Plus</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G16" t="n">
+        <v>10</v>
+      </c>
+      <c r="H16" t="n">
+        <v>11</v>
+      </c>
+      <c r="I16" t="n">
+        <v>15</v>
+      </c>
+      <c r="J16" t="n">
+        <v>22</v>
+      </c>
+      <c r="K16" t="n">
+        <v>48</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
         <v>5</v>
       </c>
-      <c r="H16" t="n">
-        <v>7</v>
-      </c>
-      <c r="I16" t="n">
-        <v>10</v>
-      </c>
-      <c r="J16" t="n">
-        <v>24</v>
-      </c>
-      <c r="K16" t="n">
-        <v>43</v>
-      </c>
-      <c r="L16" t="n">
-        <v>48</v>
-      </c>
-      <c r="M16" t="n">
-        <v>22</v>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>96000000</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1467,51 +1463,55 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>6</v>
       </c>
       <c r="H17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I17" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K17" t="n">
-        <v>42</v>
-      </c>
-      <c r="L17" t="n">
-        <v>46</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
-        <v>24</v>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="N17" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1521,50 +1521,48 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>10</v>
+      </c>
+      <c r="H18" t="n">
         <v>14</v>
       </c>
-      <c r="H18" t="n">
-        <v>24</v>
-      </c>
       <c r="I18" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J18" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K18" t="n">
-        <v>44</v>
-      </c>
-      <c r="L18" t="n">
-        <v>45</v>
-      </c>
-      <c r="M18" t="n">
-        <v>13</v>
-      </c>
-      <c r="N18" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>345741</v>
+      </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -1590,33 +1588,33 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H19" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I19" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="K19" t="n">
+        <v>43</v>
+      </c>
+      <c r="L19" t="n">
         <v>48</v>
       </c>
-      <c r="L19" t="n">
-        <v>49</v>
-      </c>
       <c r="M19" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -1629,57 +1627,51 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lotto Plus 2</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plus 2</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H20" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I20" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J20" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K20" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="L20" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="M20" t="n">
-        <v>28</v>
-      </c>
-      <c r="N20" t="n">
-        <v>7500000</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1694,12 +1686,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Lotto Plus 2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1715,25 +1707,25 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="I21" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K21" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L21" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="M21" t="n">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="N21" t="n">
-        <v>8500000</v>
+        <v>7500000</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -1749,17 +1741,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1772,25 +1764,27 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H22" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I22" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="J22" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="K22" t="n">
-        <v>21</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="n">
-        <v>340306.8</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="L22" t="n">
+        <v>49</v>
+      </c>
+      <c r="M22" t="n">
+        <v>16</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -1801,17 +1795,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lotto Plus 1</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Plus 1</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1827,31 +1821,25 @@
         <v>14</v>
       </c>
       <c r="H23" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="I23" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="J23" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="K23" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="L23" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="M23" t="n">
-        <v>41</v>
-      </c>
-      <c r="N23" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1861,49 +1849,57 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto Plus 1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H24" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="I24" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="J24" t="n">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="K24" t="n">
-        <v>30</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="L24" t="n">
+        <v>55</v>
+      </c>
+      <c r="M24" t="n">
+        <v>41</v>
+      </c>
       <c r="N24" t="n">
-        <v>394608</v>
-      </c>
-      <c r="O24" t="inlineStr"/>
+        <v>5000000</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1913,12 +1909,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1928,34 +1924,36 @@
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>12</v>
+      </c>
+      <c r="J25" t="n">
+        <v>13</v>
+      </c>
+      <c r="K25" t="n">
         <v>24</v>
       </c>
-      <c r="I25" t="n">
-        <v>29</v>
-      </c>
-      <c r="J25" t="n">
-        <v>47</v>
-      </c>
-      <c r="K25" t="n">
-        <v>48</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>58</v>
+      </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="N25" t="n">
-        <v>91000000</v>
+        <v>8500000</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -1971,55 +1969,49 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PowerBall Plus</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
+        <v>6</v>
+      </c>
+      <c r="I26" t="n">
+        <v>14</v>
+      </c>
+      <c r="J26" t="n">
+        <v>20</v>
+      </c>
+      <c r="K26" t="n">
         <v>21</v>
       </c>
-      <c r="I26" t="n">
-        <v>23</v>
-      </c>
-      <c r="J26" t="n">
-        <v>41</v>
-      </c>
-      <c r="K26" t="n">
-        <v>43</v>
-      </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="n">
-        <v>11</v>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>93000000</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>340306.8</v>
+      </c>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2258,7 +2250,7 @@
         <v>8</v>
       </c>
       <c r="Y2" t="n">
-        <v>73.94</v>
+        <v>73.72</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -2267,7 +2259,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -2299,23 +2291,23 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K3" t="n">
+        <v>21</v>
+      </c>
+      <c r="L3" t="n">
         <v>25</v>
-      </c>
-      <c r="L3" t="n">
-        <v>33</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
@@ -2324,7 +2316,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -2348,16 +2340,16 @@
         <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>47.94</v>
+        <v>47.72</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5|10|12|25|33</t>
+          <t>10|12|15|21|25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -2389,13 +2381,13 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="n">
         <v>10</v>
       </c>
-      <c r="I4" t="n">
-        <v>12</v>
-      </c>
       <c r="J4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K4" t="n">
         <v>21</v>
@@ -2405,7 +2397,7 @@
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -2414,7 +2406,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -2438,16 +2430,16 @@
         <v>5</v>
       </c>
       <c r="Y4" t="n">
-        <v>42.94</v>
+        <v>42.72</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10|12|15|21|25</t>
+          <t>6|10|13|21|25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -2479,23 +2471,23 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -2504,7 +2496,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -2528,16 +2520,16 @@
         <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>40.44</v>
+        <v>40.22</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5|6|9|22|27</t>
+          <t>4|7|10|25|35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -2569,13 +2561,13 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
         <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K6" t="n">
         <v>25</v>
@@ -2585,7 +2577,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -2594,7 +2586,7 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -2618,16 +2610,16 @@
         <v>5</v>
       </c>
       <c r="Y6" t="n">
-        <v>38.94</v>
+        <v>38.72</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5|8|14|25|27</t>
+          <t>3|8|10|25|27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -2659,32 +2651,32 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
         <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K7" t="n">
         <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -2708,16 +2700,16 @@
         <v>5</v>
       </c>
       <c r="Y7" t="n">
-        <v>37.94</v>
+        <v>37.72</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2|10|11|25|35</t>
+          <t>6|10|15|25|36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -2749,23 +2741,23 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
         <v>6</v>
       </c>
-      <c r="I8" t="n">
-        <v>10</v>
-      </c>
       <c r="J8" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L8" t="n">
         <v>27</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="O8" t="n">
         <v>3</v>
@@ -2774,7 +2766,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -2798,16 +2790,16 @@
         <v>5</v>
       </c>
       <c r="Y8" t="n">
-        <v>37.22571428571428</v>
+        <v>37.00571428571428</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6|10|15|23|27</t>
+          <t>4|6|9|25|27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -2839,32 +2831,32 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
+        <v>21</v>
+      </c>
+      <c r="L9" t="n">
         <v>25</v>
-      </c>
-      <c r="L9" t="n">
-        <v>27</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -2888,16 +2880,16 @@
         <v>5</v>
       </c>
       <c r="Y9" t="n">
-        <v>36.69</v>
+        <v>36.47</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3|8|10|25|27</t>
+          <t>4|10|14|21|25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -2929,23 +2921,23 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
         <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K10" t="n">
         <v>25</v>
       </c>
       <c r="L10" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -2954,7 +2946,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -2978,16 +2970,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>36.27333333333333</v>
+        <v>36.05333333333333</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9|10|14|25|31</t>
+          <t>6|10|11|25|33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -3019,23 +3011,23 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K11" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L11" t="n">
         <v>27</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -3044,7 +3036,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -3068,16 +3060,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>35.94</v>
+        <v>35.72</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4|6|9|25|27</t>
+          <t>7|10|12|23|27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -3109,32 +3101,32 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L12" t="n">
         <v>25</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="O12" t="n">
+        <v>3</v>
+      </c>
+      <c r="P12" t="n">
         <v>2</v>
       </c>
-      <c r="P12" t="n">
-        <v>3</v>
-      </c>
       <c r="Q12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
@@ -3158,16 +3150,16 @@
         <v>5</v>
       </c>
       <c r="Y12" t="n">
-        <v>35.66727272727273</v>
+        <v>35.44727272727273</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4|10|14|21|25</t>
+          <t>5|6|9|22|25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr"/>
@@ -3259,7 +3251,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -3353,7 +3345,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -3447,7 +3439,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -3541,7 +3533,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -3635,7 +3627,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -3729,7 +3721,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -3823,7 +3815,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -3917,7 +3909,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -4011,7 +4003,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -4105,7 +4097,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -4199,7 +4191,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB23" t="n">
@@ -4293,7 +4285,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -4385,7 +4377,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -4477,7 +4469,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -4569,7 +4561,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -4661,7 +4653,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -4753,7 +4745,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -4845,7 +4837,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -4937,7 +4929,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -5029,7 +5021,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -5121,7 +5113,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -5172,7 +5164,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -5208,16 +5200,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.4375</v>
+        <v>74.625</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|31</t>
+          <t>1|3|5|44|46|49|41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -5270,7 +5262,7 @@
         <v>46</v>
       </c>
       <c r="M35" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="N35" t="n">
         <v>148</v>
@@ -5306,16 +5298,16 @@
         <v>8</v>
       </c>
       <c r="Y35" t="n">
-        <v>74.4375</v>
+        <v>74.625</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|31</t>
+          <t>1|3|5|44|46|49|41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB35" t="n">
@@ -5353,25 +5345,25 @@
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J36" t="n">
         <v>24</v>
       </c>
       <c r="K36" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L36" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M36" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N36" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -5380,7 +5372,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -5404,20 +5396,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>48.4375</v>
+        <v>48.625</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>1|9|24|30|44|45|4</t>
+          <t>2|19|24|31|40|47|10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37">
@@ -5451,25 +5443,25 @@
         <v>11</v>
       </c>
       <c r="H37" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I37" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J37" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K37" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="L37" t="n">
+        <v>42</v>
+      </c>
+      <c r="M37" t="n">
         <v>38</v>
       </c>
-      <c r="M37" t="n">
-        <v>20</v>
-      </c>
       <c r="N37" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -5478,7 +5470,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -5502,20 +5494,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>35.9375</v>
+        <v>36.125</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>3|5|24|37|38|44|20</t>
+          <t>9|11|20|26|42|49|38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38">
@@ -5549,25 +5541,25 @@
         <v>2</v>
       </c>
       <c r="H38" t="n">
+        <v>5</v>
+      </c>
+      <c r="I38" t="n">
         <v>9</v>
       </c>
-      <c r="I38" t="n">
-        <v>16</v>
-      </c>
       <c r="J38" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K38" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L38" t="n">
         <v>44</v>
       </c>
       <c r="M38" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="N38" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -5576,7 +5568,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -5600,16 +5592,16 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>43.4375</v>
+        <v>43.625</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>9|16|22|31|44|45|7</t>
+          <t>5|9|24|30|44|45|31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB38" t="n">
@@ -5650,22 +5642,22 @@
         <v>3</v>
       </c>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="L39" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M39" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="N39" t="n">
-        <v>121</v>
+        <v>167</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -5674,7 +5666,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -5698,20 +5690,20 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>35.74519230769231</v>
+        <v>35.93269230769231</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>3|4|12|25|38|39|15</t>
+          <t>3|18|24|34|39|49|2</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40">
@@ -5745,25 +5737,25 @@
         <v>3</v>
       </c>
       <c r="H40" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I40" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K40" t="n">
         <v>26</v>
       </c>
       <c r="L40" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M40" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="N40" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -5772,7 +5764,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -5796,20 +5788,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>40.9375</v>
+        <v>41.125</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>9|11|17|26|38|40|35</t>
+          <t>6|19|24|26|31|45|8</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41">
@@ -5846,22 +5838,22 @@
         <v>3</v>
       </c>
       <c r="I41" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J41" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K41" t="n">
+        <v>34</v>
+      </c>
+      <c r="L41" t="n">
+        <v>39</v>
+      </c>
+      <c r="M41" t="n">
         <v>25</v>
       </c>
-      <c r="L41" t="n">
-        <v>38</v>
-      </c>
-      <c r="M41" t="n">
-        <v>49</v>
-      </c>
       <c r="N41" t="n">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -5870,7 +5862,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -5894,20 +5886,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>35.58035714285714</v>
+        <v>35.76785714285714</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>3|9|12|25|38|44|49</t>
+          <t>3|12|20|34|39|45|25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42">
@@ -5941,34 +5933,34 @@
         <v>4</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I42" t="n">
+        <v>16</v>
+      </c>
+      <c r="J42" t="n">
+        <v>19</v>
+      </c>
+      <c r="K42" t="n">
+        <v>37</v>
+      </c>
+      <c r="L42" t="n">
+        <v>41</v>
+      </c>
+      <c r="M42" t="n">
         <v>7</v>
       </c>
-      <c r="J42" t="n">
-        <v>24</v>
-      </c>
-      <c r="K42" t="n">
-        <v>26</v>
-      </c>
-      <c r="L42" t="n">
+      <c r="N42" t="n">
+        <v>163</v>
+      </c>
+      <c r="O42" t="n">
+        <v>3</v>
+      </c>
+      <c r="P42" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q42" t="n">
         <v>38</v>
-      </c>
-      <c r="M42" t="n">
-        <v>5</v>
-      </c>
-      <c r="N42" t="n">
-        <v>141</v>
-      </c>
-      <c r="O42" t="n">
-        <v>3</v>
-      </c>
-      <c r="P42" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>44</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -5992,20 +5984,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>39.4375</v>
+        <v>39.625</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>1|7|24|26|38|45|5</t>
+          <t>6|16|19|37|41|44|7</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43">
@@ -6042,19 +6034,19 @@
         <v>3</v>
       </c>
       <c r="I43" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J43" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="K43" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L43" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M43" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="N43" t="n">
         <v>139</v>
@@ -6066,7 +6058,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -6090,20 +6082,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>35.4375</v>
+        <v>35.625</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>3|4|24|29|34|45|27</t>
+          <t>3|6|9|34|38|49|10</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44">
@@ -6137,10 +6129,10 @@
         <v>5</v>
       </c>
       <c r="H44" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J44" t="n">
         <v>24</v>
@@ -6149,13 +6141,13 @@
         <v>33</v>
       </c>
       <c r="L44" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M44" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N44" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -6164,7 +6156,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -6188,20 +6180,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>38.4375</v>
+        <v>38.625</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>6|16|24|33|41|43|2</t>
+          <t>16|17|24|33|38|41|12</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45">
@@ -6238,22 +6230,22 @@
         <v>3</v>
       </c>
       <c r="I45" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J45" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K45" t="n">
         <v>29</v>
       </c>
       <c r="L45" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="M45" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="N45" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="O45" t="n">
         <v>3</v>
@@ -6262,7 +6254,7 @@
         <v>3</v>
       </c>
       <c r="Q45" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R45" t="n">
         <v>1</v>
@@ -6286,20 +6278,20 @@
         <v>5</v>
       </c>
       <c r="Y45" t="n">
-        <v>35.3125</v>
+        <v>35.5</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>3|4|20|29|42|45|18</t>
+          <t>3|14|21|29|38|46|24</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB45" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46">
@@ -6336,22 +6328,22 @@
         <v>2</v>
       </c>
       <c r="I46" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J46" t="n">
         <v>24</v>
       </c>
       <c r="K46" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="L46" t="n">
         <v>41</v>
       </c>
       <c r="M46" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="N46" t="n">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -6360,7 +6352,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -6384,20 +6376,20 @@
         <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>37.72321428571428</v>
+        <v>37.91071428571428</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>2|19|24|39|41|42|7</t>
+          <t>2|9|24|31|41|44|32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47">
@@ -6431,25 +6423,25 @@
         <v>16</v>
       </c>
       <c r="H47" t="n">
+        <v>3</v>
+      </c>
+      <c r="I47" t="n">
         <v>5</v>
-      </c>
-      <c r="I47" t="n">
-        <v>6</v>
       </c>
       <c r="J47" t="n">
         <v>24</v>
       </c>
       <c r="K47" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L47" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M47" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="N47" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -6458,7 +6450,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -6482,20 +6474,20 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>35.20220588235294</v>
+        <v>35.38970588235294</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>5|6|24|34|39|45|13</t>
+          <t>3|5|24|37|38|44|20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48">
@@ -6529,7 +6521,7 @@
         <v>7</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I48" t="n">
         <v>19</v>
@@ -6538,16 +6530,16 @@
         <v>24</v>
       </c>
       <c r="K48" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="L48" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="M48" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N48" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -6556,7 +6548,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -6580,20 +6572,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>37.1875</v>
+        <v>37.375</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>1|19|24|38|40|45|42</t>
+          <t>3|19|24|30|31|40|41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49">
@@ -6627,34 +6619,34 @@
         <v>17</v>
       </c>
       <c r="H49" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I49" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J49" t="n">
         <v>20</v>
       </c>
       <c r="K49" t="n">
+        <v>29</v>
+      </c>
+      <c r="L49" t="n">
+        <v>40</v>
+      </c>
+      <c r="M49" t="n">
+        <v>4</v>
+      </c>
+      <c r="N49" t="n">
+        <v>161</v>
+      </c>
+      <c r="O49" t="n">
+        <v>3</v>
+      </c>
+      <c r="P49" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q49" t="n">
         <v>31</v>
-      </c>
-      <c r="L49" t="n">
-        <v>42</v>
-      </c>
-      <c r="M49" t="n">
-        <v>10</v>
-      </c>
-      <c r="N49" t="n">
-        <v>165</v>
-      </c>
-      <c r="O49" t="n">
-        <v>3</v>
-      </c>
-      <c r="P49" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>37</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -6678,20 +6670,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.10416666666666</v>
+        <v>35.29166666666666</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>9|17|20|31|42|46|10</t>
+          <t>11|19|20|29|40|42|4</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="50">
@@ -6725,25 +6717,25 @@
         <v>8</v>
       </c>
       <c r="H50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I50" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J50" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K50" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="L50" t="n">
+        <v>32</v>
+      </c>
+      <c r="M50" t="n">
         <v>48</v>
       </c>
-      <c r="M50" t="n">
-        <v>13</v>
-      </c>
       <c r="N50" t="n">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -6752,7 +6744,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -6776,20 +6768,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>36.77083333333333</v>
+        <v>36.95833333333333</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>5|9|14|40|48|49|13</t>
+          <t>3|13|24|26|32|41|48</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="51">
@@ -6826,22 +6818,22 @@
         <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J51" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K51" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L51" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="M51" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="N51" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -6850,7 +6842,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -6874,20 +6866,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.01644736842105</v>
+        <v>35.20394736842105</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|6|24|31|34|43|11</t>
+          <t>3|12|23|34|39|40|48</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52">
@@ -6921,25 +6913,25 @@
         <v>9</v>
       </c>
       <c r="H52" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I52" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J52" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K52" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L52" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M52" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="N52" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -6948,7 +6940,7 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -6972,20 +6964,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>36.4375</v>
+        <v>36.625</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>5|9|22|30|40|45|1</t>
+          <t>17|19|24|27|38|40|33</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53">
@@ -7022,22 +7014,22 @@
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J53" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K53" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="L53" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M53" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="N53" t="n">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -7046,7 +7038,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -7070,20 +7062,20 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>34.9375</v>
+        <v>35.125</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|6|15|40|42|49|46</t>
+          <t>3|4|24|29|31|34|28</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54">
@@ -7117,25 +7109,25 @@
         <v>10</v>
       </c>
       <c r="H54" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I54" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K54" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L54" t="n">
         <v>39</v>
       </c>
       <c r="M54" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="N54" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -7144,7 +7136,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -7168,20 +7160,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>36.16477272727273</v>
+        <v>36.35227272727273</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>6|18|19|31|39|44|48</t>
+          <t>17|20|24|29|39|40|7</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55">
@@ -7218,22 +7210,22 @@
         <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J55" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K55" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L55" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M55" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="N55" t="n">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -7242,7 +7234,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -7266,20 +7258,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>34.86607142857143</v>
+        <v>35.05357142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|5|20|34|38|39|4</t>
+          <t>3|8|15|38|42|49|18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -7345,24 +7337,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="G2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
@@ -7373,7 +7365,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -7440,20 +7432,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>16</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4375</v>
+        <v>2.625</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3125</v>
+        <v>0.5625</v>
       </c>
     </row>
   </sheetData>
@@ -7490,7 +7482,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12713</t>
+          <t>12716</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7530,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-24 00:00:00</t>
+          <t>2026-05-25 00:00:00</t>
         </is>
       </c>
     </row>
@@ -7562,7 +7554,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-25 14:23:59</t>
+          <t>2026-05-26 14:14:48</t>
         </is>
       </c>
     </row>
@@ -7612,7 +7604,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UK49s: Weighted_AllHistory_v1 is currently ranked first.</t>
+          <t>UK49s: Random_Baseline is currently ranked first.</t>
         </is>
       </c>
     </row>
@@ -7636,7 +7628,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1 model/game combinations are currently beating Random_Baseline.</t>
+          <t>0 model/game combinations are currently beating Random_Baseline.</t>
         </is>
       </c>
     </row>
@@ -7774,7 +7766,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -7784,34 +7776,34 @@
         <v>16</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8217</v>
+        <v>0.7733</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8317</v>
+        <v>0.795</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
         <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>2.5</v>
+        <v>2.8125</v>
       </c>
       <c r="L2" t="n">
-        <v>2.4375</v>
+        <v>2.625</v>
       </c>
       <c r="M2" t="n">
         <v>16</v>
       </c>
       <c r="N2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3125</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="3">
@@ -7828,7 +7820,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -7838,34 +7830,34 @@
         <v>16</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7167</v>
+        <v>0.695</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7267</v>
+        <v>0.7017</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3125</v>
+        <v>2.5</v>
       </c>
       <c r="L3" t="n">
-        <v>2.3125</v>
+        <v>2.4375</v>
       </c>
       <c r="M3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>0.375</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="4">
@@ -7882,7 +7874,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -7892,10 +7884,10 @@
         <v>16</v>
       </c>
       <c r="G4" t="n">
-        <v>0.615</v>
+        <v>0.905</v>
       </c>
       <c r="H4" t="n">
-        <v>0.625</v>
+        <v>0.9233</v>
       </c>
       <c r="I4" t="n">
         <v>3</v>
@@ -7904,22 +7896,22 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1875</v>
+        <v>2.5</v>
       </c>
       <c r="L4" t="n">
-        <v>2.1875</v>
+        <v>2.4375</v>
       </c>
       <c r="M4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3125</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
@@ -7936,7 +7928,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -7946,34 +7938,34 @@
         <v>16</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6917</v>
+        <v>0.6883</v>
       </c>
       <c r="H5" t="n">
-        <v>0.705</v>
+        <v>0.695</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>2.125</v>
+        <v>2.4375</v>
       </c>
       <c r="L5" t="n">
-        <v>2.125</v>
+        <v>2.375</v>
       </c>
       <c r="M5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N5" t="n">
+        <v>5</v>
+      </c>
+      <c r="O5" t="n">
         <v>4</v>
       </c>
-      <c r="O5" t="n">
-        <v>3</v>
-      </c>
       <c r="P5" t="n">
-        <v>0.1875</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="6">
@@ -7990,7 +7982,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -8000,28 +7992,28 @@
         <v>16</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6483</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6633</v>
+        <v>0.71</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>2.125</v>
+        <v>2.4375</v>
       </c>
       <c r="L6" t="n">
-        <v>2.0625</v>
+        <v>2.3125</v>
       </c>
       <c r="M6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
         <v>6</v>
@@ -8054,34 +8046,34 @@
         <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>0.65</v>
+        <v>0.6983</v>
       </c>
       <c r="H7" t="n">
-        <v>0.665</v>
+        <v>0.7117</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="8">
@@ -8090,7 +8082,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -8108,10 +8100,10 @@
         <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>0.708</v>
+        <v>0.671</v>
       </c>
       <c r="H8" t="n">
-        <v>0.708</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="I8" t="n">
         <v>3</v>
@@ -8120,19 +8112,23 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="L8" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="M8" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="N8" t="n">
-        <v>19</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="O8" t="n">
+        <v>16</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -8144,11 +8140,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -8158,34 +8154,34 @@
         <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>0.671</v>
+        <v>0.596</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.612</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="M9" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="N9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="10">
@@ -8198,11 +8194,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -8212,10 +8208,10 @@
         <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>0.596</v>
+        <v>0.658</v>
       </c>
       <c r="H10" t="n">
-        <v>0.612</v>
+        <v>0.676</v>
       </c>
       <c r="I10" t="n">
         <v>4</v>
@@ -8224,16 +8220,16 @@
         <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="L10" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="M10" t="n">
         <v>64</v>
       </c>
       <c r="N10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O10" t="n">
         <v>15</v>
@@ -8252,7 +8248,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -8266,28 +8262,28 @@
         <v>100</v>
       </c>
       <c r="G11" t="n">
-        <v>0.742</v>
+        <v>0.752</v>
       </c>
       <c r="H11" t="n">
-        <v>0.742</v>
+        <v>0.752</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="L11" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="M11" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N11" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -8298,15 +8294,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -8316,35 +8312,31 @@
         <v>100</v>
       </c>
       <c r="G12" t="n">
-        <v>0.658</v>
+        <v>0.681</v>
       </c>
       <c r="H12" t="n">
-        <v>0.676</v>
+        <v>0.681</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="L12" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="M12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N12" t="n">
-        <v>11</v>
-      </c>
-      <c r="O12" t="n">
-        <v>15</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.15</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -8406,15 +8398,15 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -8424,10 +8416,10 @@
         <v>100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.616</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>0.632</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="I14" t="n">
         <v>3</v>
@@ -8436,23 +8428,19 @@
         <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="L14" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="M14" t="n">
         <v>57</v>
       </c>
       <c r="N14" t="n">
-        <v>9</v>
-      </c>
-      <c r="O14" t="n">
-        <v>12</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.12</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -8464,11 +8452,11 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -8478,28 +8466,28 @@
         <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.671</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.671</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="L15" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="M15" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -8510,11 +8498,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -8528,10 +8516,10 @@
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.674</v>
+        <v>0.616</v>
       </c>
       <c r="H16" t="n">
-        <v>0.674</v>
+        <v>0.632</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
@@ -8540,19 +8528,23 @@
         <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="L16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="M16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N16" t="n">
         <v>9</v>
       </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>12</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -8622,7 +8614,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -8632,10 +8624,10 @@
         <v>100</v>
       </c>
       <c r="G18" t="n">
-        <v>0.704</v>
+        <v>0.674</v>
       </c>
       <c r="H18" t="n">
-        <v>0.704</v>
+        <v>0.674</v>
       </c>
       <c r="I18" t="n">
         <v>3</v>
@@ -8644,16 +8636,16 @@
         <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="L18" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="M18" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -8672,7 +8664,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -8682,10 +8674,10 @@
         <v>100</v>
       </c>
       <c r="G19" t="n">
-        <v>0.698</v>
+        <v>0.664</v>
       </c>
       <c r="H19" t="n">
-        <v>0.698</v>
+        <v>0.664</v>
       </c>
       <c r="I19" t="n">
         <v>3</v>
@@ -8694,16 +8686,16 @@
         <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="L19" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="M19" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -9130,7 +9122,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -9142,7 +9134,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -9152,35 +9144,35 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>0.708</v>
+        <v>0.752</v>
       </c>
       <c r="H2" t="n">
-        <v>0.708</v>
+        <v>0.752</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="L2" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="M2" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="N2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -9300,7 +9292,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -9310,34 +9302,34 @@
         <v>16</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8217</v>
+        <v>0.7733</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8317</v>
+        <v>0.795</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5</v>
+        <v>2.8125</v>
       </c>
       <c r="L5" t="n">
-        <v>2.4375</v>
+        <v>2.625</v>
       </c>
       <c r="M5" t="n">
         <v>16</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3125</v>
+        <v>0.5625</v>
       </c>
     </row>
   </sheetData>
@@ -9399,20 +9391,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="D2" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -9428,20 +9420,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="D3" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.18</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -9457,20 +9449,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="D4" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.29</v>
+        <v>-0.04</v>
       </c>
       <c r="F4" t="n">
-        <v>-9</v>
+        <v>5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -9490,16 +9482,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="D5" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.29</v>
+        <v>-0.05</v>
       </c>
       <c r="F5" t="n">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -9515,20 +9507,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="D6" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.31</v>
+        <v>-0.08</v>
       </c>
       <c r="F6" t="n">
-        <v>-11</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -9544,20 +9536,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="D7" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.36</v>
+        <v>-0.09</v>
       </c>
       <c r="F7" t="n">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -9921,24 +9913,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.4375</v>
+        <v>2.625</v>
       </c>
       <c r="D20" t="n">
-        <v>2.3125</v>
+        <v>2.625</v>
       </c>
       <c r="E20" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9950,20 +9942,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.3125</v>
+        <v>2.4375</v>
       </c>
       <c r="D21" t="n">
-        <v>2.3125</v>
+        <v>2.625</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>-0.1875</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -9979,20 +9971,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.1875</v>
+        <v>2.4375</v>
       </c>
       <c r="D22" t="n">
-        <v>2.3125</v>
+        <v>2.625</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.125</v>
+        <v>-0.1875</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -10008,20 +10000,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2.125</v>
+        <v>2.375</v>
       </c>
       <c r="D23" t="n">
-        <v>2.3125</v>
+        <v>2.625</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1875</v>
+        <v>-0.25</v>
       </c>
       <c r="F23" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -10037,20 +10029,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.0625</v>
+        <v>2.3125</v>
       </c>
       <c r="D24" t="n">
-        <v>2.3125</v>
+        <v>2.625</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.25</v>
+        <v>-0.3125</v>
       </c>
       <c r="F24" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -10070,16 +10062,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="D25" t="n">
-        <v>2.3125</v>
+        <v>2.625</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.3125</v>
+        <v>-0.375</v>
       </c>
       <c r="F25" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>

--- a/data/exports/reporting/daily_lottery_summary.xlsx
+++ b/data/exports/reporting/daily_lottery_summary.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:49</t>
+          <t>2026-05-27 14:58:41</t>
         </is>
       </c>
     </row>
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12716</v>
+        <v>12721</v>
       </c>
     </row>
     <row r="4">
@@ -480,7 +480,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
     </row>
@@ -654,32 +654,32 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="J2" t="n">
         <v>25</v>
       </c>
       <c r="K2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>359265</v>
+        <v>469540.4</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -706,33 +706,33 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H3" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I3" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J3" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="K3" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M3" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -745,12 +745,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -760,34 +760,40 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" s="1" t="n">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J4" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="K4" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>3</v>
+      </c>
       <c r="N4" t="n">
-        <v>300000</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
+        <v>107000000</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -797,51 +803,55 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>PowerBall Plus</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" s="1" t="n">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="I5" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J5" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="K5" t="n">
-        <v>28</v>
-      </c>
-      <c r="L5" t="n">
-        <v>45</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>41</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="N5" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -856,43 +866,43 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" t="n">
+        <v>11</v>
+      </c>
+      <c r="J6" t="n">
+        <v>24</v>
+      </c>
+      <c r="K6" t="n">
+        <v>31</v>
+      </c>
+      <c r="L6" t="n">
+        <v>36</v>
+      </c>
+      <c r="M6" t="n">
         <v>9</v>
-      </c>
-      <c r="H6" t="n">
-        <v>17</v>
-      </c>
-      <c r="I6" t="n">
-        <v>24</v>
-      </c>
-      <c r="J6" t="n">
-        <v>36</v>
-      </c>
-      <c r="K6" t="n">
-        <v>38</v>
-      </c>
-      <c r="L6" t="n">
-        <v>49</v>
-      </c>
-      <c r="M6" t="n">
-        <v>4</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -920,32 +930,32 @@
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" s="1" t="n">
-        <v>46165</v>
+        <v>46167</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="J7" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K7" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>364517.7</v>
+        <v>359265</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -957,57 +967,51 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" s="1" t="n">
-        <v>46165</v>
+        <v>46167</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="I8" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="J8" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="K8" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="M8" t="n">
-        <v>34</v>
-      </c>
-      <c r="N8" t="n">
-        <v>10500000</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1017,57 +1021,51 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lotto Plus 1</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plus 1</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L9" t="n">
+        <v>45</v>
+      </c>
+      <c r="M9" t="n">
         <v>41</v>
       </c>
-      <c r="M9" t="n">
-        <v>52</v>
-      </c>
-      <c r="N9" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1077,57 +1075,49 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lotto Plus 2</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Plus 2</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I10" t="n">
+        <v>12</v>
+      </c>
+      <c r="J10" t="n">
         <v>23</v>
       </c>
-      <c r="J10" t="n">
-        <v>30</v>
-      </c>
       <c r="K10" t="n">
-        <v>33</v>
-      </c>
-      <c r="L10" t="n">
-        <v>47</v>
-      </c>
-      <c r="M10" t="n">
-        <v>19</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>8500000</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>300000</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1152,33 +1142,33 @@
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H11" t="n">
+        <v>17</v>
+      </c>
+      <c r="I11" t="n">
         <v>24</v>
       </c>
-      <c r="I11" t="n">
-        <v>40</v>
-      </c>
       <c r="J11" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="K11" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="L11" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1191,17 +1181,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>Lotto Plus 2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Plus 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1214,28 +1204,34 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K12" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L12" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="M12" t="n">
-        <v>49</v>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="N12" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1250,43 +1246,43 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H13" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="I13" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="J13" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K13" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L13" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="M13" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1304,40 +1300,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="J14" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="K14" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="L14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M14" t="n">
         <v>9</v>
@@ -1368,32 +1364,32 @@
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K15" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>474917.1</v>
+        <v>364517.7</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -1405,49 +1401,51 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PowerBall Plus</t>
+          <t>Lotto Plus 1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Plus 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H16" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I16" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K16" t="n">
-        <v>48</v>
-      </c>
-      <c r="L16" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="L16" t="n">
+        <v>41</v>
+      </c>
       <c r="M16" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="N16" t="n">
-        <v>96000000</v>
+        <v>6000000</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1463,12 +1461,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1478,34 +1476,36 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H17" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="J17" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="K17" t="n">
-        <v>25</v>
-      </c>
-      <c r="L17" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="L17" t="n">
+        <v>53</v>
+      </c>
       <c r="M17" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="N17" t="n">
-        <v>100000000</v>
+        <v>10500000</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1536,32 +1536,32 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I18" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K18" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
-        <v>345741</v>
+        <v>474917.1</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -1573,51 +1573,55 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I19" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K19" t="n">
-        <v>43</v>
-      </c>
-      <c r="L19" t="n">
-        <v>48</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>22</v>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="N19" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1627,51 +1631,55 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>PowerBall Plus</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H20" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I20" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J20" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K20" t="n">
-        <v>42</v>
-      </c>
-      <c r="L20" t="n">
-        <v>46</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
-        <v>24</v>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="N20" t="n">
+        <v>96000000</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1681,57 +1689,51 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lotto Plus 2</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Plus 2</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I21" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J21" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K21" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="L21" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="M21" t="n">
-        <v>28</v>
-      </c>
-      <c r="N21" t="n">
-        <v>7500000</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1746,43 +1748,43 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>12</v>
+      </c>
+      <c r="K22" t="n">
+        <v>20</v>
+      </c>
+      <c r="L22" t="n">
+        <v>46</v>
+      </c>
+      <c r="M22" t="n">
         <v>9</v>
-      </c>
-      <c r="H22" t="n">
-        <v>19</v>
-      </c>
-      <c r="I22" t="n">
-        <v>31</v>
-      </c>
-      <c r="J22" t="n">
-        <v>34</v>
-      </c>
-      <c r="K22" t="n">
-        <v>48</v>
-      </c>
-      <c r="L22" t="n">
-        <v>49</v>
-      </c>
-      <c r="M22" t="n">
-        <v>16</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -1795,50 +1797,48 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G23" t="n">
+        <v>10</v>
+      </c>
+      <c r="H23" t="n">
         <v>14</v>
       </c>
-      <c r="H23" t="n">
-        <v>24</v>
-      </c>
       <c r="I23" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J23" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K23" t="n">
-        <v>44</v>
-      </c>
-      <c r="L23" t="n">
-        <v>45</v>
-      </c>
-      <c r="M23" t="n">
-        <v>13</v>
-      </c>
-      <c r="N23" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>345741</v>
+      </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -1849,57 +1849,51 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lotto Plus 1</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Plus 1</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H24" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="I24" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="K24" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="L24" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="M24" t="n">
-        <v>41</v>
-      </c>
-      <c r="N24" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1909,57 +1903,51 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I25" t="n">
         <v>12</v>
       </c>
       <c r="J25" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="K25" t="n">
+        <v>42</v>
+      </c>
+      <c r="L25" t="n">
+        <v>46</v>
+      </c>
+      <c r="M25" t="n">
         <v>24</v>
       </c>
-      <c r="L25" t="n">
-        <v>58</v>
-      </c>
-      <c r="M25" t="n">
-        <v>53</v>
-      </c>
-      <c r="N25" t="n">
-        <v>8500000</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2250,7 +2238,7 @@
         <v>8</v>
       </c>
       <c r="Y2" t="n">
-        <v>73.72</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -2259,7 +2247,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -2291,23 +2279,23 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I3" t="n">
         <v>10</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>12</v>
       </c>
-      <c r="J3" t="n">
-        <v>15</v>
-      </c>
       <c r="K3" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
@@ -2316,7 +2304,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -2340,16 +2328,16 @@
         <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>47.72</v>
+        <v>47.9</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10|12|15|21|25</t>
+          <t>7|10|12|25|27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -2381,23 +2369,23 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -2406,7 +2394,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -2430,16 +2418,16 @@
         <v>5</v>
       </c>
       <c r="Y4" t="n">
-        <v>42.72</v>
+        <v>42.9</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6|10|13|21|25</t>
+          <t>5|10|12|25|33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -2474,20 +2462,20 @@
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
         <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -2496,7 +2484,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -2520,16 +2508,16 @@
         <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>40.22</v>
+        <v>40.4</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4|7|10|25|35</t>
+          <t>4|5|6|25|27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -2561,13 +2549,13 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K6" t="n">
         <v>25</v>
@@ -2577,7 +2565,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -2586,7 +2574,7 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -2610,16 +2598,16 @@
         <v>5</v>
       </c>
       <c r="Y6" t="n">
-        <v>38.72</v>
+        <v>38.9</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3|8|10|25|27</t>
+          <t>6|10|13|25|27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -2651,32 +2639,32 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
         <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L7" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="O7" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" t="n">
         <v>2</v>
       </c>
-      <c r="P7" t="n">
-        <v>3</v>
-      </c>
       <c r="Q7" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -2700,16 +2688,16 @@
         <v>5</v>
       </c>
       <c r="Y7" t="n">
-        <v>37.72</v>
+        <v>37.9</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6|10|15|25|36</t>
+          <t>5|10|12|23|27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -2741,13 +2729,13 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="n">
         <v>4</v>
       </c>
-      <c r="I8" t="n">
-        <v>6</v>
-      </c>
       <c r="J8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K8" t="n">
         <v>25</v>
@@ -2757,7 +2745,7 @@
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O8" t="n">
         <v>3</v>
@@ -2766,7 +2754,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -2790,16 +2778,16 @@
         <v>5</v>
       </c>
       <c r="Y8" t="n">
-        <v>37.00571428571428</v>
+        <v>37.18571428571428</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4|6|9|25|27</t>
+          <t>3|4|10|25|27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -2834,29 +2822,29 @@
         <v>4</v>
       </c>
       <c r="I9" t="n">
+        <v>7</v>
+      </c>
+      <c r="J9" t="n">
         <v>10</v>
       </c>
-      <c r="J9" t="n">
-        <v>14</v>
-      </c>
       <c r="K9" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L9" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="n">
         <v>2</v>
       </c>
-      <c r="P9" t="n">
-        <v>3</v>
-      </c>
       <c r="Q9" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -2880,16 +2868,16 @@
         <v>5</v>
       </c>
       <c r="Y9" t="n">
-        <v>36.47</v>
+        <v>36.65</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4|10|14|21|25</t>
+          <t>4|7|10|25|35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -2924,20 +2912,20 @@
         <v>6</v>
       </c>
       <c r="I10" t="n">
+        <v>9</v>
+      </c>
+      <c r="J10" t="n">
         <v>10</v>
       </c>
-      <c r="J10" t="n">
-        <v>11</v>
-      </c>
       <c r="K10" t="n">
+        <v>21</v>
+      </c>
+      <c r="L10" t="n">
         <v>25</v>
-      </c>
-      <c r="L10" t="n">
-        <v>33</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -2946,7 +2934,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -2970,16 +2958,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>36.05333333333333</v>
+        <v>36.23333333333333</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6|10|11|25|33</t>
+          <t>6|9|10|21|25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -3011,23 +2999,23 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
         <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -3036,7 +3024,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -3060,16 +3048,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>35.72</v>
+        <v>35.9</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7|10|12|23|27</t>
+          <t>9|10|14|25|31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -3101,32 +3089,32 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L12" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
@@ -3150,16 +3138,16 @@
         <v>5</v>
       </c>
       <c r="Y12" t="n">
-        <v>35.44727272727273</v>
+        <v>35.62727272727273</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5|6|9|22|25</t>
+          <t>6|10|15|25|36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr"/>
@@ -3251,7 +3239,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -3345,7 +3333,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -3439,7 +3427,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -3533,7 +3521,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -3627,7 +3615,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -3721,7 +3709,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -3815,7 +3803,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -3909,7 +3897,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -4003,7 +3991,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -4097,7 +4085,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -4191,7 +4179,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB23" t="n">
@@ -4276,7 +4264,7 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>57.58</v>
+        <v>57.59</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -4285,7 +4273,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -4317,25 +4305,25 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K25" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L25" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M25" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="N25" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -4344,7 +4332,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -4365,19 +4353,19 @@
         <v>0.5</v>
       </c>
       <c r="X25" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>55.58</v>
+        <v>52.59</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11|16|20|31|41|5</t>
+          <t>15|19|24|29|42|18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -4409,25 +4397,25 @@
         <v>4</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I26" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K26" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L26" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M26" t="n">
         <v>5</v>
       </c>
       <c r="N26" t="n">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -4436,7 +4424,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -4460,16 +4448,16 @@
         <v>8</v>
       </c>
       <c r="Y26" t="n">
-        <v>51.58</v>
+        <v>51.59</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>1|13|18|34|37|5</t>
+          <t>11|16|20|31|41|5</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -4498,28 +4486,28 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I27" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K27" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L27" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="M27" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="N27" t="n">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -4528,7 +4516,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -4537,7 +4525,7 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="U27" t="n">
         <v>0.5</v>
@@ -4549,19 +4537,19 @@
         <v>0.5</v>
       </c>
       <c r="X27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>50.58</v>
+        <v>50.09</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>2|9|19|31|34|2</t>
+          <t>16|19|22|29|43|11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -4590,28 +4578,28 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H28" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J28" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="K28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L28" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M28" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="N28" t="n">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="O28" t="n">
         <v>3</v>
@@ -4620,7 +4608,7 @@
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -4629,7 +4617,7 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="U28" t="n">
         <v>0.5</v>
@@ -4641,19 +4629,19 @@
         <v>0.5</v>
       </c>
       <c r="X28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y28" t="n">
-        <v>50.08</v>
+        <v>49.34</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15|20|24|29|39|11</t>
+          <t>1|12|13|28|37|18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -4682,28 +4670,28 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K29" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L29" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M29" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N29" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -4712,7 +4700,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -4721,7 +4709,7 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U29" t="n">
         <v>0.5</v>
@@ -4736,16 +4724,16 @@
         <v>8</v>
       </c>
       <c r="Y29" t="n">
-        <v>49.33</v>
+        <v>48.92333333333333</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>7|19|24|34|37|13</t>
+          <t>10|20|23|31|41|15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -4777,22 +4765,22 @@
         <v>9</v>
       </c>
       <c r="H30" t="n">
+        <v>7</v>
+      </c>
+      <c r="I30" t="n">
+        <v>19</v>
+      </c>
+      <c r="J30" t="n">
+        <v>24</v>
+      </c>
+      <c r="K30" t="n">
+        <v>34</v>
+      </c>
+      <c r="L30" t="n">
+        <v>37</v>
+      </c>
+      <c r="M30" t="n">
         <v>12</v>
-      </c>
-      <c r="I30" t="n">
-        <v>15</v>
-      </c>
-      <c r="J30" t="n">
-        <v>20</v>
-      </c>
-      <c r="K30" t="n">
-        <v>29</v>
-      </c>
-      <c r="L30" t="n">
-        <v>45</v>
-      </c>
-      <c r="M30" t="n">
-        <v>11</v>
       </c>
       <c r="N30" t="n">
         <v>121</v>
@@ -4804,7 +4792,7 @@
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -4828,16 +4816,16 @@
         <v>8</v>
       </c>
       <c r="Y30" t="n">
-        <v>48.58</v>
+        <v>48.59</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12|15|20|29|45|11</t>
+          <t>7|19|24|34|37|12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -4866,28 +4854,28 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H31" t="n">
         <v>11</v>
       </c>
       <c r="I31" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J31" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K31" t="n">
         <v>28</v>
       </c>
       <c r="L31" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="M31" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N31" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -4896,7 +4884,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -4905,7 +4893,7 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U31" t="n">
         <v>0.5</v>
@@ -4917,19 +4905,19 @@
         <v>0.5</v>
       </c>
       <c r="X31" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y31" t="n">
-        <v>46.86571428571428</v>
+        <v>48.31727272727273</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11|19|24|28|31|3</t>
+          <t>11|13|20|28|39|18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -4958,28 +4946,28 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H32" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I32" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J32" t="n">
         <v>24</v>
       </c>
       <c r="K32" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="L32" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N32" t="n">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -4988,7 +4976,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -4997,7 +4985,7 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U32" t="n">
         <v>0.5</v>
@@ -5012,16 +5000,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>45.91333333333333</v>
+        <v>47.59</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>9|15|24|29|36|1</t>
+          <t>17|19|24|26|43|3</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -5050,28 +5038,28 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H33" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I33" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J33" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K33" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L33" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="M33" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="N33" t="n">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="O33" t="n">
         <v>3</v>
@@ -5080,7 +5068,7 @@
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -5089,7 +5077,7 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U33" t="n">
         <v>0.5</v>
@@ -5104,16 +5092,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>45.30727272727272</v>
+        <v>46.87571428571429</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>9|19|24|34|35|18</t>
+          <t>13|15|20|29|30|2</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -5164,7 +5152,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -5200,16 +5188,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.625</v>
+        <v>74.75</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|41</t>
+          <t>1|3|5|44|46|49|34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -5262,7 +5250,7 @@
         <v>46</v>
       </c>
       <c r="M35" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="N35" t="n">
         <v>148</v>
@@ -5298,16 +5286,16 @@
         <v>8</v>
       </c>
       <c r="Y35" t="n">
-        <v>74.625</v>
+        <v>74.75</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|41</t>
+          <t>1|3|5|44|46|49|34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB35" t="n">
@@ -5345,25 +5333,25 @@
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I36" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J36" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K36" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L36" t="n">
         <v>40</v>
       </c>
       <c r="M36" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N36" t="n">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -5372,7 +5360,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -5396,20 +5384,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>48.625</v>
+        <v>48.75</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>2|19|24|31|40|47|10</t>
+          <t>9|10|17|26|40|41|6</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37">
@@ -5440,28 +5428,28 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H37" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>20</v>
       </c>
       <c r="K37" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="L37" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M37" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="N37" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -5470,7 +5458,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -5479,7 +5467,7 @@
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -5491,19 +5479,19 @@
         <v>0.5</v>
       </c>
       <c r="X37" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y37" t="n">
-        <v>36.125</v>
+        <v>38.89285714285714</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>9|11|20|26|42|49|38</t>
+          <t>1|2|20|42|45|49|9</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB37" t="n">
@@ -5541,25 +5529,25 @@
         <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I38" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K38" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="L38" t="n">
         <v>44</v>
       </c>
       <c r="M38" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="N38" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -5568,7 +5556,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -5592,20 +5580,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>43.625</v>
+        <v>43.75</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>5|9|24|30|44|45|31</t>
+          <t>2|16|19|37|44|49|26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39">
@@ -5636,28 +5624,28 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H39" t="n">
         <v>3</v>
       </c>
       <c r="I39" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J39" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K39" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L39" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M39" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="N39" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -5675,7 +5663,7 @@
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -5690,16 +5678,16 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>35.93269230769231</v>
+        <v>36.25</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>3|18|24|34|39|49|2</t>
+          <t>3|8|23|38|44|49|40</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB39" t="n">
@@ -5737,25 +5725,25 @@
         <v>3</v>
       </c>
       <c r="H40" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I40" t="n">
         <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K40" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L40" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="M40" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="N40" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -5764,7 +5752,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -5788,16 +5776,16 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>41.125</v>
+        <v>41.25</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>6|19|24|26|31|45|8</t>
+          <t>7|19|20|30|44|45|15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB40" t="n">
@@ -5832,28 +5820,28 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H41" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I41" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J41" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K41" t="n">
+        <v>31</v>
+      </c>
+      <c r="L41" t="n">
         <v>34</v>
       </c>
-      <c r="L41" t="n">
-        <v>39</v>
-      </c>
       <c r="M41" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N41" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -5862,7 +5850,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -5871,7 +5859,7 @@
         <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -5886,20 +5874,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>35.76785714285714</v>
+        <v>36.05769230769231</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>3|12|20|34|39|45|25</t>
+          <t>6|15|24|31|34|49|27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42">
@@ -5933,25 +5921,25 @@
         <v>4</v>
       </c>
       <c r="H42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J42" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K42" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="L42" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M42" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="N42" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -5960,7 +5948,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -5984,20 +5972,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>39.625</v>
+        <v>39.75</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>6|16|19|37|41|44|7</t>
+          <t>5|9|24|30|44|45|32</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43">
@@ -6034,22 +6022,22 @@
         <v>3</v>
       </c>
       <c r="I43" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J43" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K43" t="n">
         <v>34</v>
       </c>
       <c r="L43" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M43" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="N43" t="n">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -6058,7 +6046,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -6082,20 +6070,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>35.625</v>
+        <v>35.75</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>3|6|9|34|38|49|10</t>
+          <t>3|12|20|34|39|45|24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44">
@@ -6129,25 +6117,25 @@
         <v>5</v>
       </c>
       <c r="H44" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I44" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
         <v>24</v>
       </c>
       <c r="K44" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="L44" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M44" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N44" t="n">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -6156,7 +6144,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -6180,20 +6168,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>38.625</v>
+        <v>38.75</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16|17|24|33|38|41|12</t>
+          <t>6|19|24|26|31|45|8</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45">
@@ -6230,22 +6218,22 @@
         <v>3</v>
       </c>
       <c r="I45" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J45" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="K45" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L45" t="n">
         <v>38</v>
       </c>
       <c r="M45" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="N45" t="n">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="O45" t="n">
         <v>3</v>
@@ -6254,7 +6242,7 @@
         <v>3</v>
       </c>
       <c r="Q45" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="R45" t="n">
         <v>1</v>
@@ -6278,20 +6266,20 @@
         <v>5</v>
       </c>
       <c r="Y45" t="n">
-        <v>35.5</v>
+        <v>35.625</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>3|14|21|29|38|46|24</t>
+          <t>3|6|9|34|38|49|10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB45" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46">
@@ -6325,25 +6313,25 @@
         <v>6</v>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I46" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J46" t="n">
         <v>24</v>
       </c>
       <c r="K46" t="n">
+        <v>26</v>
+      </c>
+      <c r="L46" t="n">
         <v>31</v>
       </c>
-      <c r="L46" t="n">
-        <v>41</v>
-      </c>
       <c r="M46" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="N46" t="n">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -6352,7 +6340,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -6376,20 +6364,20 @@
         <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>37.91071428571428</v>
+        <v>38.03571428571428</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>2|9|24|31|41|44|32</t>
+          <t>17|19|24|26|31|46|4</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="47">
@@ -6426,7 +6414,7 @@
         <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="J47" t="n">
         <v>24</v>
@@ -6438,10 +6426,10 @@
         <v>38</v>
       </c>
       <c r="M47" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="N47" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -6450,7 +6438,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -6474,20 +6462,20 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>35.38970588235294</v>
+        <v>35.51470588235294</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|5|24|37|38|44|20</t>
+          <t>3|17|24|37|38|46|49</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48">
@@ -6521,25 +6509,25 @@
         <v>7</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="I48" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J48" t="n">
         <v>24</v>
       </c>
       <c r="K48" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L48" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="M48" t="n">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="N48" t="n">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -6548,7 +6536,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -6572,20 +6560,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>37.375</v>
+        <v>37.5</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3|19|24|30|31|40|41</t>
+          <t>16|17|24|33|38|41|12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="49">
@@ -6670,7 +6658,7 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.29166666666666</v>
+        <v>35.41666666666666</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
@@ -6679,7 +6667,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB49" t="n">
@@ -6717,25 +6705,25 @@
         <v>8</v>
       </c>
       <c r="H50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I50" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J50" t="n">
         <v>24</v>
       </c>
       <c r="K50" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="L50" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="M50" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="N50" t="n">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -6744,7 +6732,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -6768,20 +6756,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>36.95833333333333</v>
+        <v>37.08333333333333</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|13|24|26|32|41|48</t>
+          <t>2|9|24|40|43|45|33</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51">
@@ -6818,22 +6806,22 @@
         <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J51" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="K51" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L51" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M51" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="N51" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -6842,7 +6830,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -6866,20 +6854,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.20394736842105</v>
+        <v>35.32894736842105</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|12|23|34|39|40|48</t>
+          <t>3|4|11|38|44|49|1</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52">
@@ -6913,34 +6901,34 @@
         <v>9</v>
       </c>
       <c r="H52" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I52" t="n">
+        <v>16</v>
+      </c>
+      <c r="J52" t="n">
         <v>19</v>
       </c>
-      <c r="J52" t="n">
-        <v>24</v>
-      </c>
       <c r="K52" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="L52" t="n">
+        <v>41</v>
+      </c>
+      <c r="M52" t="n">
+        <v>7</v>
+      </c>
+      <c r="N52" t="n">
+        <v>163</v>
+      </c>
+      <c r="O52" t="n">
+        <v>3</v>
+      </c>
+      <c r="P52" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q52" t="n">
         <v>38</v>
-      </c>
-      <c r="M52" t="n">
-        <v>33</v>
-      </c>
-      <c r="N52" t="n">
-        <v>165</v>
-      </c>
-      <c r="O52" t="n">
-        <v>3</v>
-      </c>
-      <c r="P52" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>23</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -6964,20 +6952,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>36.625</v>
+        <v>36.75</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17|19|24|27|38|40|33</t>
+          <t>6|16|19|37|41|44|7</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="53">
@@ -7011,25 +6999,25 @@
         <v>19</v>
       </c>
       <c r="H53" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I53" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K53" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L53" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M53" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="N53" t="n">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -7038,7 +7026,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -7062,20 +7050,20 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.125</v>
+        <v>35.25</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|4|24|29|31|34|28</t>
+          <t>10|19|20|28|35|45|5</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54">
@@ -7109,25 +7097,25 @@
         <v>10</v>
       </c>
       <c r="H54" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I54" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J54" t="n">
         <v>24</v>
       </c>
       <c r="K54" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L54" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="M54" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="N54" t="n">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -7136,7 +7124,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -7160,16 +7148,16 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>36.35227272727273</v>
+        <v>36.47727272727273</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17|20|24|29|39|40|7</t>
+          <t>3|19|24|30|31|40|41</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -7207,25 +7195,25 @@
         <v>20</v>
       </c>
       <c r="H55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I55" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J55" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K55" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L55" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="M55" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="N55" t="n">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -7234,7 +7222,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -7258,20 +7246,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>35.05357142857143</v>
+        <v>35.17857142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|8|15|38|42|49|18</t>
+          <t>5|11|20|32|37|44|12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -7337,24 +7325,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="G2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
@@ -7365,7 +7353,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -7395,7 +7383,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
@@ -7409,13 +7397,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="5">
@@ -7432,20 +7420,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>16</v>
       </c>
       <c r="F5" t="n">
-        <v>2.625</v>
+        <v>2.75</v>
       </c>
       <c r="G5" t="n">
         <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -7482,7 +7470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12716</t>
+          <t>12721</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7518,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-25 00:00:00</t>
+          <t>2026-05-26 00:00:00</t>
         </is>
       </c>
     </row>
@@ -7554,7 +7542,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-26 14:14:48</t>
+          <t>2026-05-27 14:48:18</t>
         </is>
       </c>
     </row>
@@ -7604,7 +7592,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UK49s: Random_Baseline is currently ranked first.</t>
+          <t>UK49s: AntiCrowding_Recent50 is currently ranked first.</t>
         </is>
       </c>
     </row>
@@ -7628,7 +7616,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0 model/game combinations are currently beating Random_Baseline.</t>
+          <t>2 model/game combinations are currently beating Random_Baseline.</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7754,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -7776,22 +7764,22 @@
         <v>16</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7733</v>
+        <v>0.7917</v>
       </c>
       <c r="H2" t="n">
-        <v>0.795</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
         <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>2.8125</v>
+        <v>2.75</v>
       </c>
       <c r="L2" t="n">
-        <v>2.625</v>
+        <v>2.75</v>
       </c>
       <c r="M2" t="n">
         <v>16</v>
@@ -7800,10 +7788,10 @@
         <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3">
@@ -7820,7 +7808,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -7830,34 +7818,34 @@
         <v>16</v>
       </c>
       <c r="G3" t="n">
-        <v>0.695</v>
+        <v>0.8383</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7017</v>
+        <v>0.86</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5</v>
+        <v>2.6875</v>
       </c>
       <c r="L3" t="n">
-        <v>2.4375</v>
+        <v>2.625</v>
       </c>
       <c r="M3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1875</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="4">
@@ -7874,7 +7862,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -7884,28 +7872,28 @@
         <v>16</v>
       </c>
       <c r="G4" t="n">
-        <v>0.905</v>
+        <v>0.7017</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9233</v>
+        <v>0.7233000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5</v>
+        <v>2.625</v>
       </c>
       <c r="L4" t="n">
         <v>2.4375</v>
       </c>
       <c r="M4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O4" t="n">
         <v>8</v>
@@ -7928,7 +7916,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -7941,13 +7929,13 @@
         <v>0.6883</v>
       </c>
       <c r="H5" t="n">
-        <v>0.695</v>
+        <v>0.7117</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
         <v>2.4375</v>
@@ -7956,16 +7944,16 @@
         <v>2.375</v>
       </c>
       <c r="M5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P5" t="n">
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="6">
@@ -7982,7 +7970,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -7992,34 +7980,34 @@
         <v>16</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7267</v>
       </c>
       <c r="H6" t="n">
-        <v>0.71</v>
+        <v>0.7467</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>2.4375</v>
+        <v>2.375</v>
       </c>
       <c r="L6" t="n">
         <v>2.3125</v>
       </c>
       <c r="M6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N6" t="n">
         <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P6" t="n">
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
@@ -8046,10 +8034,10 @@
         <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6983</v>
+        <v>0.72</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7117</v>
+        <v>0.7367</v>
       </c>
       <c r="I7" t="n">
         <v>4</v>
@@ -8082,7 +8070,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -8100,10 +8088,10 @@
         <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>0.671</v>
+        <v>0.699</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.699</v>
       </c>
       <c r="I8" t="n">
         <v>3</v>
@@ -8112,23 +8100,19 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="L8" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="N8" t="n">
-        <v>11</v>
-      </c>
-      <c r="O8" t="n">
         <v>16</v>
       </c>
-      <c r="P8" t="n">
-        <v>0.16</v>
-      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -8140,11 +8124,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -8154,34 +8138,34 @@
         <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>0.596</v>
+        <v>0.671</v>
       </c>
       <c r="H9" t="n">
-        <v>0.612</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="L9" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="M9" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="N9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P9" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="10">
@@ -8194,11 +8178,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -8208,10 +8192,10 @@
         <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>0.658</v>
+        <v>0.596</v>
       </c>
       <c r="H10" t="n">
-        <v>0.676</v>
+        <v>0.612</v>
       </c>
       <c r="I10" t="n">
         <v>4</v>
@@ -8220,16 +8204,16 @@
         <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="M10" t="n">
         <v>64</v>
       </c>
       <c r="N10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O10" t="n">
         <v>15</v>
@@ -8244,15 +8228,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -8262,10 +8246,10 @@
         <v>100</v>
       </c>
       <c r="G11" t="n">
-        <v>0.752</v>
+        <v>0.658</v>
       </c>
       <c r="H11" t="n">
-        <v>0.752</v>
+        <v>0.676</v>
       </c>
       <c r="I11" t="n">
         <v>4</v>
@@ -8274,19 +8258,23 @@
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="L11" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="M11" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="N11" t="n">
-        <v>13</v>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="O11" t="n">
+        <v>15</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -8302,7 +8290,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -8312,10 +8300,10 @@
         <v>100</v>
       </c>
       <c r="G12" t="n">
-        <v>0.681</v>
+        <v>0.753</v>
       </c>
       <c r="H12" t="n">
-        <v>0.681</v>
+        <v>0.753</v>
       </c>
       <c r="I12" t="n">
         <v>3</v>
@@ -8324,16 +8312,16 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="L12" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="M12" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="N12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
@@ -8344,15 +8332,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -8362,35 +8350,31 @@
         <v>100</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>0.612</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="L13" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="M13" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N13" t="n">
-        <v>11</v>
-      </c>
-      <c r="O13" t="n">
-        <v>8</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.08</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -8402,11 +8386,11 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -8416,10 +8400,10 @@
         <v>100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.704</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.704</v>
       </c>
       <c r="I14" t="n">
         <v>3</v>
@@ -8428,13 +8412,13 @@
         <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="L14" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="M14" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="N14" t="n">
         <v>11</v>
@@ -8448,7 +8432,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -8456,7 +8440,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -8466,10 +8450,10 @@
         <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>0.671</v>
+        <v>0.6</v>
       </c>
       <c r="H15" t="n">
-        <v>0.671</v>
+        <v>0.612</v>
       </c>
       <c r="I15" t="n">
         <v>4</v>
@@ -8478,19 +8462,23 @@
         <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="L15" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="M15" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N15" t="n">
         <v>11</v>
       </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>8</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -8552,11 +8540,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -8570,10 +8558,10 @@
         <v>100</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>0.614</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="I17" t="n">
         <v>3</v>
@@ -8582,23 +8570,19 @@
         <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="L17" t="n">
         <v>1.65</v>
       </c>
       <c r="M17" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
-      </c>
-      <c r="O17" t="n">
-        <v>10</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0.1</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -8606,15 +8590,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -8624,10 +8608,10 @@
         <v>100</v>
       </c>
       <c r="G18" t="n">
-        <v>0.674</v>
+        <v>0.6</v>
       </c>
       <c r="H18" t="n">
-        <v>0.674</v>
+        <v>0.614</v>
       </c>
       <c r="I18" t="n">
         <v>3</v>
@@ -8636,19 +8620,23 @@
         <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="L18" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N18" t="n">
-        <v>7</v>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="O18" t="n">
+        <v>10</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -8656,15 +8644,15 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -8674,31 +8662,35 @@
         <v>100</v>
       </c>
       <c r="G19" t="n">
-        <v>0.664</v>
+        <v>0.521</v>
       </c>
       <c r="H19" t="n">
-        <v>0.664</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="I19" t="n">
         <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="L19" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="M19" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="N19" t="n">
-        <v>11</v>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="O19" t="n">
+        <v>35</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.35</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -8706,15 +8698,15 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -8724,35 +8716,31 @@
         <v>100</v>
       </c>
       <c r="G20" t="n">
-        <v>0.498</v>
+        <v>0.656</v>
       </c>
       <c r="H20" t="n">
-        <v>0.541</v>
+        <v>0.656</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J20" t="n">
         <v>4</v>
       </c>
       <c r="K20" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="L20" t="n">
         <v>1.58</v>
       </c>
       <c r="M20" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N20" t="n">
-        <v>9</v>
-      </c>
-      <c r="O20" t="n">
-        <v>36</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0.36</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -8768,7 +8756,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -8778,34 +8766,34 @@
         <v>100</v>
       </c>
       <c r="G21" t="n">
-        <v>0.556</v>
+        <v>0.535</v>
       </c>
       <c r="H21" t="n">
-        <v>0.598</v>
+        <v>0.587</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
         <v>4</v>
       </c>
       <c r="K21" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="L21" t="n">
         <v>1.56</v>
       </c>
       <c r="M21" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O21" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="P21" t="n">
-        <v>0.29</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="22">
@@ -8832,10 +8820,10 @@
         <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>0.473</v>
+        <v>0.491</v>
       </c>
       <c r="H22" t="n">
-        <v>0.52</v>
+        <v>0.542</v>
       </c>
       <c r="I22" t="n">
         <v>3</v>
@@ -8844,22 +8832,22 @@
         <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="L22" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="M22" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="N22" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P22" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="23">
@@ -8876,7 +8864,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -8886,34 +8874,34 @@
         <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>0.469</v>
+        <v>0.521</v>
       </c>
       <c r="H23" t="n">
-        <v>0.53</v>
+        <v>0.573</v>
       </c>
       <c r="I23" t="n">
         <v>3</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="L23" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M23" t="n">
         <v>43</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O23" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="P23" t="n">
-        <v>0.41</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="24">
@@ -8930,7 +8918,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -8940,34 +8928,34 @@
         <v>100</v>
       </c>
       <c r="G24" t="n">
-        <v>0.514</v>
+        <v>0.536</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.585</v>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
         <v>4</v>
       </c>
       <c r="K24" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="L24" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="M24" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O24" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P24" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="25">
@@ -8984,7 +8972,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -8994,10 +8982,10 @@
         <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.475</v>
+        <v>0.51</v>
       </c>
       <c r="H25" t="n">
-        <v>0.528</v>
+        <v>0.55</v>
       </c>
       <c r="I25" t="n">
         <v>3</v>
@@ -9006,22 +8994,22 @@
         <v>3</v>
       </c>
       <c r="K25" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="L25" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="M25" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="N25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O25" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P25" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -9122,7 +9110,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -9134,7 +9122,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -9144,35 +9132,35 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>0.752</v>
+        <v>0.699</v>
       </c>
       <c r="H2" t="n">
-        <v>0.752</v>
+        <v>0.699</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="M2" t="n">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="N2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -9226,7 +9214,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -9248,10 +9236,10 @@
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>0.498</v>
+        <v>0.521</v>
       </c>
       <c r="H4" t="n">
-        <v>0.541</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="I4" t="n">
         <v>3</v>
@@ -9260,22 +9248,22 @@
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="L4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M4" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="N4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P4" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="5">
@@ -9292,7 +9280,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -9302,22 +9290,22 @@
         <v>16</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7733</v>
+        <v>0.7917</v>
       </c>
       <c r="H5" t="n">
-        <v>0.795</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8125</v>
+        <v>2.75</v>
       </c>
       <c r="L5" t="n">
-        <v>2.625</v>
+        <v>2.75</v>
       </c>
       <c r="M5" t="n">
         <v>16</v>
@@ -9326,10 +9314,10 @@
         <v>10</v>
       </c>
       <c r="O5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -9391,20 +9379,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="D2" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -9420,20 +9408,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="D3" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -9449,20 +9437,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="D4" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.04</v>
+        <v>-0.18</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>-6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -9478,20 +9466,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="D5" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -9507,20 +9495,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="D6" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.08</v>
+        <v>-0.25</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -9540,16 +9528,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="D7" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.09</v>
+        <v>-0.32</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>-8</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -9743,10 +9731,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="D14" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -9768,20 +9756,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1.56</v>
       </c>
       <c r="D15" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="F15" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -9801,13 +9789,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="D16" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.11</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F16" t="n">
         <v>-2</v>
@@ -9826,20 +9814,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="D17" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="E17" t="n">
         <v>-0.12</v>
       </c>
       <c r="F17" t="n">
-        <v>-6</v>
+        <v>2</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -9855,20 +9843,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="D18" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="F18" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -9884,20 +9872,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="D19" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.24</v>
+        <v>-0.16</v>
       </c>
       <c r="F19" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -9913,24 +9901,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.625</v>
+        <v>2.75</v>
       </c>
       <c r="D20" t="n">
-        <v>2.625</v>
+        <v>2.4375</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>0.3125</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -9942,24 +9930,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C21" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="D21" t="n">
         <v>2.4375</v>
       </c>
-      <c r="D21" t="n">
-        <v>2.625</v>
-      </c>
       <c r="E21" t="n">
-        <v>-0.1875</v>
+        <v>0.1875</v>
       </c>
       <c r="F21" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -9971,20 +9959,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>2.4375</v>
       </c>
       <c r="D22" t="n">
-        <v>2.625</v>
+        <v>2.4375</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1875</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -10000,20 +9988,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>2.375</v>
       </c>
       <c r="D23" t="n">
-        <v>2.625</v>
+        <v>2.4375</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.25</v>
+        <v>-0.0625</v>
       </c>
       <c r="F23" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -10029,20 +10017,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>2.3125</v>
       </c>
       <c r="D24" t="n">
-        <v>2.625</v>
+        <v>2.4375</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3125</v>
+        <v>-0.125</v>
       </c>
       <c r="F24" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -10065,13 +10053,13 @@
         <v>2.25</v>
       </c>
       <c r="D25" t="n">
-        <v>2.625</v>
+        <v>2.4375</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.375</v>
+        <v>-0.1875</v>
       </c>
       <c r="F25" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>

--- a/data/exports/reporting/daily_lottery_summary.xlsx
+++ b/data/exports/reporting/daily_lottery_summary.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:41</t>
+          <t>2026-05-28 08:54:45</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr"/>
@@ -3179,25 +3179,25 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
+        <v>44</v>
+      </c>
+      <c r="K13" t="n">
+        <v>49</v>
+      </c>
+      <c r="L13" t="n">
+        <v>52</v>
+      </c>
+      <c r="M13" t="n">
         <v>8</v>
       </c>
-      <c r="K13" t="n">
-        <v>44</v>
-      </c>
-      <c r="L13" t="n">
-        <v>47</v>
-      </c>
-      <c r="M13" t="n">
-        <v>23</v>
-      </c>
       <c r="N13" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="O13" t="n">
         <v>2</v>
@@ -3206,7 +3206,7 @@
         <v>4</v>
       </c>
       <c r="Q13" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -3234,16 +3234,16 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2|6|8|44|47|49|23</t>
+          <t>1|4|44|49|52|56|8</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14">
@@ -3273,34 +3273,34 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J14" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="K14" t="n">
+        <v>31</v>
+      </c>
+      <c r="L14" t="n">
+        <v>37</v>
+      </c>
+      <c r="M14" t="n">
+        <v>28</v>
+      </c>
+      <c r="N14" t="n">
+        <v>157</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q14" t="n">
         <v>43</v>
-      </c>
-      <c r="L14" t="n">
-        <v>47</v>
-      </c>
-      <c r="M14" t="n">
-        <v>12</v>
-      </c>
-      <c r="N14" t="n">
-        <v>151</v>
-      </c>
-      <c r="O14" t="n">
-        <v>3</v>
-      </c>
-      <c r="P14" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>46</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
@@ -3328,16 +3328,16 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2|3|8|43|47|48|12</t>
+          <t>6|12|22|31|37|49|28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
@@ -3367,25 +3367,25 @@
         <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I15" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J15" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="K15" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="L15" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="M15" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="N15" t="n">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="O15" t="n">
         <v>3</v>
@@ -3394,7 +3394,7 @@
         <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -3422,16 +3422,16 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2|17|23|27|40|44|32</t>
+          <t>13|14|29|32|35|46|6</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16">
@@ -3464,22 +3464,22 @@
         <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J16" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K16" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L16" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="M16" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N16" t="n">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
@@ -3488,7 +3488,7 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
@@ -3516,16 +3516,16 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>4|8|29|33|35|44|13</t>
+          <t>4|7|27|39|44|48|17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17">
@@ -3555,25 +3555,25 @@
         <v>4</v>
       </c>
       <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
         <v>2</v>
-      </c>
-      <c r="I17" t="n">
-        <v>7</v>
       </c>
       <c r="J17" t="n">
         <v>29</v>
       </c>
       <c r="K17" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="L17" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M17" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="N17" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="O17" t="n">
         <v>3</v>
@@ -3582,7 +3582,7 @@
         <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -3610,16 +3610,16 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2|7|29|33|40|46|13</t>
+          <t>1|2|29|40|42|49|34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I18" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J18" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K18" t="n">
         <v>33</v>
@@ -3664,10 +3664,10 @@
         <v>40</v>
       </c>
       <c r="M18" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="N18" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="O18" t="n">
         <v>3</v>
@@ -3704,16 +3704,16 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>4|8|27|33|40|43|20</t>
+          <t>8|12|29|33|40|47|41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19">
@@ -3743,25 +3743,25 @@
         <v>6</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J19" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K19" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M19" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="N19" t="n">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="O19" t="n">
         <v>3</v>
@@ -3770,7 +3770,7 @@
         <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
@@ -3798,16 +3798,16 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1|16|17|33|40|42|18</t>
+          <t>11|12|22|37|42|49|43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20">
@@ -3837,25 +3837,25 @@
         <v>7</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J20" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K20" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L20" t="n">
         <v>42</v>
       </c>
       <c r="M20" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="N20" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="O20" t="n">
         <v>3</v>
@@ -3864,7 +3864,7 @@
         <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
@@ -3892,16 +3892,16 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1|8|27|32|42|45|10</t>
+          <t>9|10|22|37|42|49|55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21">
@@ -3931,25 +3931,25 @@
         <v>8</v>
       </c>
       <c r="H21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I21" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J21" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K21" t="n">
         <v>30</v>
       </c>
       <c r="L21" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="M21" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="N21" t="n">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="O21" t="n">
         <v>3</v>
@@ -3958,7 +3958,7 @@
         <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
@@ -3986,16 +3986,16 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>8|17|19|30|42|49|24</t>
+          <t>7|9|22|30|33|46|55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22">
@@ -4025,25 +4025,25 @@
         <v>9</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J22" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K22" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L22" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="M22" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="N22" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="O22" t="n">
         <v>3</v>
@@ -4052,7 +4052,7 @@
         <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
@@ -4080,16 +4080,16 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2|3|24|43|44|47|10</t>
+          <t>3|13|18|32|36|49|53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB22" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23">
@@ -4119,25 +4119,25 @@
         <v>10</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J23" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K23" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="L23" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="M23" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="N23" t="n">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="O23" t="n">
         <v>3</v>
@@ -4146,7 +4146,7 @@
         <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="R23" t="n">
         <v>1</v>
@@ -4174,16 +4174,16 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1|13|14|30|32|47|21</t>
+          <t>8|12|17|37|41|48|6</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB23" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -4365,7 +4365,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB35" t="n">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB36" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB37" t="n">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB38" t="n">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB39" t="n">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB40" t="n">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB41" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB42" t="n">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB43" t="n">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB44" t="n">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB48" t="n">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB49" t="n">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB50" t="n">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB51" t="n">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB52" t="n">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB55" t="n">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-27 14:48:18</t>
+          <t>2026-05-28 08:46:33</t>
         </is>
       </c>
     </row>

--- a/data/exports/reporting/daily_lottery_summary.xlsx
+++ b/data/exports/reporting/daily_lottery_summary.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:45</t>
+          <t>2026-05-28 17:22:52</t>
         </is>
       </c>
     </row>
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12721</v>
+        <v>12728</v>
       </c>
     </row>
     <row r="4">
@@ -480,7 +480,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
     </row>
@@ -654,24 +654,24 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K2" t="n">
         <v>32</v>
@@ -679,7 +679,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>469540.4</v>
+        <v>396450</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -706,33 +706,33 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H3" t="n">
         <v>17</v>
       </c>
       <c r="I3" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="J3" t="n">
+        <v>35</v>
+      </c>
+      <c r="K3" t="n">
         <v>36</v>
       </c>
-      <c r="K3" t="n">
-        <v>38</v>
-      </c>
       <c r="L3" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M3" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -745,55 +745,51 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J4" t="n">
         <v>31</v>
       </c>
       <c r="K4" t="n">
-        <v>47</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
+        <v>37</v>
+      </c>
+      <c r="L4" t="n">
+        <v>40</v>
+      </c>
       <c r="M4" t="n">
-        <v>3</v>
-      </c>
-      <c r="N4" t="n">
-        <v>107000000</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -803,49 +799,51 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PowerBall Plus</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H5" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I5" t="n">
         <v>29</v>
       </c>
       <c r="J5" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K5" t="n">
-        <v>37</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="L5" t="n">
+        <v>56</v>
+      </c>
       <c r="M5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="N5" t="n">
-        <v>100000000</v>
+        <v>13000000</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -861,51 +859,57 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>Lotto Plus 2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Plus 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" s="1" t="n">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
         <v>11</v>
       </c>
       <c r="J6" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K6" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L6" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="M6" t="n">
-        <v>9</v>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+        <v>51</v>
+      </c>
+      <c r="N6" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -915,49 +919,57 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto Plus 1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" s="1" t="n">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="J7" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="K7" t="n">
-        <v>36</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="L7" t="n">
+        <v>58</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3</v>
+      </c>
       <c r="N7" t="n">
-        <v>359265</v>
-      </c>
-      <c r="O7" t="inlineStr"/>
+        <v>7000000</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -967,50 +979,48 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I8" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J8" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="K8" t="n">
-        <v>25</v>
-      </c>
-      <c r="L8" t="n">
-        <v>41</v>
-      </c>
-      <c r="M8" t="n">
-        <v>7</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>469540.4</v>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1026,43 +1036,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" s="1" t="n">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H9" t="n">
         <v>17</v>
       </c>
       <c r="I9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J9" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="K9" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="L9" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="M9" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1075,48 +1085,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" s="1" t="n">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I10" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J10" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="K10" t="n">
-        <v>31</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
-        <v>300000</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="L10" t="n">
+        <v>44</v>
+      </c>
+      <c r="M10" t="n">
+        <v>35</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1127,51 +1139,55 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" s="1" t="n">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
         <v>9</v>
       </c>
-      <c r="H11" t="n">
-        <v>17</v>
-      </c>
       <c r="I11" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J11" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K11" t="n">
-        <v>38</v>
-      </c>
-      <c r="L11" t="n">
-        <v>49</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>4</v>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N11" t="n">
+        <v>107000000</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1181,51 +1197,49 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lotto Plus 2</t>
+          <t>PowerBall Plus</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plus 2</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" s="1" t="n">
-        <v>46165</v>
+        <v>46168</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H12" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="I12" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K12" t="n">
-        <v>33</v>
-      </c>
-      <c r="L12" t="n">
-        <v>47</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="N12" t="n">
-        <v>8500000</v>
+        <v>100000000</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1256,33 +1270,33 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" s="1" t="n">
-        <v>46165</v>
+        <v>46167</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" t="n">
+        <v>11</v>
+      </c>
+      <c r="J13" t="n">
+        <v>24</v>
+      </c>
+      <c r="K13" t="n">
+        <v>31</v>
+      </c>
+      <c r="L13" t="n">
+        <v>36</v>
+      </c>
+      <c r="M13" t="n">
         <v>9</v>
-      </c>
-      <c r="H13" t="n">
-        <v>22</v>
-      </c>
-      <c r="I13" t="n">
-        <v>28</v>
-      </c>
-      <c r="J13" t="n">
-        <v>29</v>
-      </c>
-      <c r="K13" t="n">
-        <v>35</v>
-      </c>
-      <c r="L13" t="n">
-        <v>38</v>
-      </c>
-      <c r="M13" t="n">
-        <v>49</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1295,50 +1309,48 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" s="1" t="n">
-        <v>46165</v>
+        <v>46167</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I14" t="n">
         <v>8</v>
       </c>
-      <c r="H14" t="n">
-        <v>24</v>
-      </c>
-      <c r="I14" t="n">
-        <v>40</v>
-      </c>
       <c r="J14" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="K14" t="n">
-        <v>46</v>
-      </c>
-      <c r="L14" t="n">
-        <v>47</v>
-      </c>
-      <c r="M14" t="n">
-        <v>9</v>
-      </c>
-      <c r="N14" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>359265</v>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1349,48 +1361,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" s="1" t="n">
-        <v>46165</v>
+        <v>46167</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I15" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J15" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="K15" t="n">
-        <v>31</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
-        <v>364517.7</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="L15" t="n">
+        <v>41</v>
+      </c>
+      <c r="M15" t="n">
+        <v>7</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -1401,57 +1415,51 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lotto Plus 1</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plus 1</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>9</v>
       </c>
       <c r="H16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="K16" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="L16" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M16" t="n">
-        <v>52</v>
-      </c>
-      <c r="N16" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1461,57 +1469,51 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="H17" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="I17" t="n">
+        <v>24</v>
+      </c>
+      <c r="J17" t="n">
+        <v>26</v>
+      </c>
+      <c r="K17" t="n">
+        <v>28</v>
+      </c>
+      <c r="L17" t="n">
         <v>45</v>
       </c>
-      <c r="J17" t="n">
-        <v>47</v>
-      </c>
-      <c r="K17" t="n">
-        <v>49</v>
-      </c>
-      <c r="L17" t="n">
-        <v>53</v>
-      </c>
       <c r="M17" t="n">
-        <v>34</v>
-      </c>
-      <c r="N17" t="n">
-        <v>10500000</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1536,32 +1538,32 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" s="1" t="n">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I18" t="n">
+        <v>12</v>
+      </c>
+      <c r="J18" t="n">
         <v>23</v>
       </c>
-      <c r="J18" t="n">
-        <v>24</v>
-      </c>
       <c r="K18" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
-        <v>474917.1</v>
+        <v>300000</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -1573,12 +1575,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1588,40 +1590,34 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H19" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K19" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="n">
-        <v>18</v>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>364517.7</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1631,49 +1627,51 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PowerBall Plus</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="H20" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="I20" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="J20" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="K20" t="n">
-        <v>48</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="L20" t="n">
+        <v>53</v>
+      </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="N20" t="n">
-        <v>96000000</v>
+        <v>10500000</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1689,51 +1687,57 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>Lotto Plus 1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Plus 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H21" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I21" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K21" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="L21" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="M21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+        <v>52</v>
+      </c>
+      <c r="N21" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1743,51 +1747,57 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>Lotto Plus 2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Plus 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I22" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K22" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="L22" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M22" t="n">
-        <v>9</v>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="N22" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1797,48 +1807,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" s="1" t="n">
-        <v>46163</v>
+        <v>46165</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H23" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I23" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="J23" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="K23" t="n">
-        <v>28</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="n">
-        <v>345741</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="L23" t="n">
+        <v>47</v>
+      </c>
+      <c r="M23" t="n">
+        <v>9</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -1854,43 +1866,43 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" s="1" t="n">
-        <v>46163</v>
+        <v>46165</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H24" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="I24" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="J24" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K24" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L24" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="M24" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
@@ -1908,43 +1920,43 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I25" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J25" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K25" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L25" t="n">
         <v>46</v>
       </c>
       <c r="M25" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
@@ -1957,48 +1969,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J26" t="n">
+        <v>12</v>
+      </c>
+      <c r="K26" t="n">
         <v>20</v>
       </c>
-      <c r="K26" t="n">
-        <v>21</v>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="n">
-        <v>340306.8</v>
-      </c>
+      <c r="L26" t="n">
+        <v>46</v>
+      </c>
+      <c r="M26" t="n">
+        <v>9</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -2238,7 +2252,7 @@
         <v>8</v>
       </c>
       <c r="Y2" t="n">
-        <v>73.90000000000001</v>
+        <v>73.84</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -2247,7 +2261,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -2282,10 +2296,10 @@
         <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
         <v>25</v>
@@ -2295,7 +2309,7 @@
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
@@ -2328,16 +2342,16 @@
         <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>47.9</v>
+        <v>47.84</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7|10|12|25|27</t>
+          <t>7|12|14|25|27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -2369,7 +2383,7 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
@@ -2381,11 +2395,11 @@
         <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -2394,7 +2408,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -2418,16 +2432,16 @@
         <v>5</v>
       </c>
       <c r="Y4" t="n">
-        <v>42.9</v>
+        <v>42.84</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5|10|12|25|33</t>
+          <t>1|10|12|25|27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -2459,23 +2473,23 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L5" t="n">
         <v>27</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -2484,7 +2498,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -2508,16 +2522,16 @@
         <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>40.4</v>
+        <v>40.34</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4|5|6|25|27</t>
+          <t>5|10|12|23|27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -2549,19 +2563,19 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" t="n">
         <v>10</v>
-      </c>
-      <c r="J6" t="n">
-        <v>13</v>
       </c>
       <c r="K6" t="n">
         <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
@@ -2574,7 +2588,7 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -2598,16 +2612,16 @@
         <v>5</v>
       </c>
       <c r="Y6" t="n">
-        <v>38.9</v>
+        <v>38.84</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6|10|13|25|27</t>
+          <t>4|7|10|25|35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -2639,23 +2653,23 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L7" t="n">
         <v>27</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -2664,7 +2678,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -2688,16 +2702,16 @@
         <v>5</v>
       </c>
       <c r="Y7" t="n">
-        <v>37.9</v>
+        <v>37.84</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5|10|12|23|27</t>
+          <t>6|13|14|25|27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -2729,23 +2743,23 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K8" t="n">
         <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="O8" t="n">
         <v>3</v>
@@ -2754,7 +2768,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -2778,16 +2792,16 @@
         <v>5</v>
       </c>
       <c r="Y8" t="n">
-        <v>37.18571428571428</v>
+        <v>37.12571428571429</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3|4|10|25|27</t>
+          <t>2|10|11|25|35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -2819,19 +2833,19 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L9" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
@@ -2844,7 +2858,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -2868,16 +2882,16 @@
         <v>5</v>
       </c>
       <c r="Y9" t="n">
-        <v>36.65</v>
+        <v>36.59</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4|7|10|25|35</t>
+          <t>6|10|15|23|27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -2909,23 +2923,23 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J10" t="n">
         <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -2934,7 +2948,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -2958,16 +2972,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>36.23333333333333</v>
+        <v>36.17333333333333</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6|9|10|21|25</t>
+          <t>3|8|10|25|27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -2999,23 +3013,23 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" t="n">
         <v>9</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>10</v>
       </c>
-      <c r="J11" t="n">
-        <v>14</v>
-      </c>
       <c r="K11" t="n">
+        <v>21</v>
+      </c>
+      <c r="L11" t="n">
         <v>25</v>
-      </c>
-      <c r="L11" t="n">
-        <v>31</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -3024,7 +3038,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -3048,16 +3062,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>35.9</v>
+        <v>35.84</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9|10|14|25|31</t>
+          <t>6|9|10|21|25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -3089,32 +3103,32 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I12" t="n">
         <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
+        <v>23</v>
+      </c>
+      <c r="L12" t="n">
         <v>25</v>
-      </c>
-      <c r="L12" t="n">
-        <v>36</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="O12" t="n">
+        <v>3</v>
+      </c>
+      <c r="P12" t="n">
         <v>2</v>
       </c>
-      <c r="P12" t="n">
-        <v>3</v>
-      </c>
       <c r="Q12" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
@@ -3138,16 +3152,16 @@
         <v>5</v>
       </c>
       <c r="Y12" t="n">
-        <v>35.62727272727273</v>
+        <v>35.56727272727272</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6|10|15|25|36</t>
+          <t>7|10|14|23|25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr"/>
@@ -3194,7 +3208,7 @@
         <v>52</v>
       </c>
       <c r="M13" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="N13" t="n">
         <v>206</v>
@@ -3230,16 +3244,16 @@
         <v>8</v>
       </c>
       <c r="Y13" t="n">
-        <v>73.81</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1|4|44|49|52|56|8</t>
+          <t>1|4|44|49|52|56|14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -3273,7 +3287,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I14" t="n">
         <v>12</v>
@@ -3282,16 +3296,16 @@
         <v>22</v>
       </c>
       <c r="K14" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L14" t="n">
         <v>37</v>
       </c>
       <c r="M14" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N14" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
@@ -3300,7 +3314,7 @@
         <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
@@ -3324,16 +3338,16 @@
         <v>5</v>
       </c>
       <c r="Y14" t="n">
-        <v>47.81</v>
+        <v>47.85</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>6|12|22|31|37|49|28</t>
+          <t>11|12|22|32|37|49|21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -3367,25 +3381,25 @@
         <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J15" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L15" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M15" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="N15" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="O15" t="n">
         <v>3</v>
@@ -3394,7 +3408,7 @@
         <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -3418,20 +3432,20 @@
         <v>5</v>
       </c>
       <c r="Y15" t="n">
-        <v>42.81</v>
+        <v>42.85</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13|14|29|32|35|46|6</t>
+          <t>7|12|23|33|40|48|42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -3461,25 +3475,25 @@
         <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I16" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J16" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="K16" t="n">
+        <v>32</v>
+      </c>
+      <c r="L16" t="n">
         <v>39</v>
       </c>
-      <c r="L16" t="n">
-        <v>44</v>
-      </c>
       <c r="M16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N16" t="n">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
@@ -3488,7 +3502,7 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
@@ -3512,20 +3526,20 @@
         <v>5</v>
       </c>
       <c r="Y16" t="n">
-        <v>40.31</v>
+        <v>40.35</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>4|7|27|39|44|48|17</t>
+          <t>8|13|18|32|39|47|16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17">
@@ -3555,25 +3569,25 @@
         <v>4</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J17" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L17" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M17" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="N17" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="O17" t="n">
         <v>3</v>
@@ -3582,7 +3596,7 @@
         <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -3606,20 +3620,20 @@
         <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>38.81</v>
+        <v>38.85</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1|2|29|40|42|49|34</t>
+          <t>2|8|23|38|43|47|16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18">
@@ -3649,22 +3663,22 @@
         <v>5</v>
       </c>
       <c r="H18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J18" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="K18" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="L18" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M18" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="N18" t="n">
         <v>169</v>
@@ -3676,7 +3690,7 @@
         <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -3700,16 +3714,16 @@
         <v>5</v>
       </c>
       <c r="Y18" t="n">
-        <v>37.81</v>
+        <v>37.85</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8|12|29|33|40|47|41</t>
+          <t>7|11|20|40|44|47|27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -3743,25 +3757,25 @@
         <v>6</v>
       </c>
       <c r="H19" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
         <v>12</v>
       </c>
       <c r="J19" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K19" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L19" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M19" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="N19" t="n">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="O19" t="n">
         <v>3</v>
@@ -3770,7 +3784,7 @@
         <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
@@ -3794,16 +3808,16 @@
         <v>5</v>
       </c>
       <c r="Y19" t="n">
-        <v>37.09571428571429</v>
+        <v>37.13571428571429</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11|12|22|37|42|49|43</t>
+          <t>1|12|15|36|40|49|9</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -3837,25 +3851,25 @@
         <v>7</v>
       </c>
       <c r="H20" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J20" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K20" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L20" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M20" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="N20" t="n">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="O20" t="n">
         <v>3</v>
@@ -3864,7 +3878,7 @@
         <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
@@ -3888,20 +3902,20 @@
         <v>5</v>
       </c>
       <c r="Y20" t="n">
-        <v>36.56</v>
+        <v>36.6</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>9|10|22|37|42|49|55</t>
+          <t>5|8|27|32|41|46|43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21">
@@ -3931,25 +3945,25 @@
         <v>8</v>
       </c>
       <c r="H21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J21" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K21" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="L21" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="M21" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="N21" t="n">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="O21" t="n">
         <v>3</v>
@@ -3958,7 +3972,7 @@
         <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
@@ -3982,20 +3996,20 @@
         <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>36.14333333333333</v>
+        <v>36.18333333333334</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>7|9|22|30|33|46|55</t>
+          <t>8|11|15|36|42|49|28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22">
@@ -4025,13 +4039,13 @@
         <v>9</v>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J22" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="K22" t="n">
         <v>32</v>
@@ -4040,10 +4054,10 @@
         <v>36</v>
       </c>
       <c r="M22" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="N22" t="n">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="O22" t="n">
         <v>3</v>
@@ -4052,7 +4066,7 @@
         <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
@@ -4076,16 +4090,16 @@
         <v>5</v>
       </c>
       <c r="Y22" t="n">
-        <v>35.81</v>
+        <v>35.85</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3|13|18|32|36|49|53</t>
+          <t>8|15|27|32|36|49|12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -4119,25 +4133,25 @@
         <v>10</v>
       </c>
       <c r="H23" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J23" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K23" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L23" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M23" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="N23" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="O23" t="n">
         <v>3</v>
@@ -4146,7 +4160,7 @@
         <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="R23" t="n">
         <v>1</v>
@@ -4170,16 +4184,16 @@
         <v>5</v>
       </c>
       <c r="Y23" t="n">
-        <v>35.53727272727272</v>
+        <v>35.57727272727273</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>8|12|17|37|41|48|6</t>
+          <t>3|7|21|32|40|48|15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB23" t="n">
@@ -4273,7 +4287,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -4365,7 +4379,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -4457,7 +4471,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -4549,7 +4563,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -4641,7 +4655,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -4733,7 +4747,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -4825,7 +4839,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -4917,7 +4931,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -5009,7 +5023,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -5101,7 +5115,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -5152,7 +5166,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -5188,16 +5202,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.75</v>
+        <v>74.86669999999999</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|34</t>
+          <t>1|3|5|44|46|49|32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -5250,7 +5264,7 @@
         <v>46</v>
       </c>
       <c r="M35" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N35" t="n">
         <v>148</v>
@@ -5286,16 +5300,16 @@
         <v>8</v>
       </c>
       <c r="Y35" t="n">
-        <v>74.75</v>
+        <v>74.86669999999999</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|34</t>
+          <t>1|3|5|44|46|49|32</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB35" t="n">
@@ -5333,25 +5347,25 @@
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I36" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K36" t="n">
         <v>26</v>
       </c>
       <c r="L36" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M36" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="N36" t="n">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -5360,7 +5374,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -5384,20 +5398,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>48.75</v>
+        <v>48.8667</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>9|10|17|26|40|41|6</t>
+          <t>17|19|24|26|38|45|39</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37">
@@ -5428,28 +5442,28 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J37" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K37" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L37" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M37" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="N37" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -5458,7 +5472,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -5467,7 +5481,7 @@
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -5479,19 +5493,19 @@
         <v>0.5</v>
       </c>
       <c r="X37" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>38.89285714285714</v>
+        <v>36.3667</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>1|2|20|42|45|49|9</t>
+          <t>3|8|23|38|44|49|39</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB37" t="n">
@@ -5529,25 +5543,25 @@
         <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I38" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J38" t="n">
         <v>19</v>
       </c>
       <c r="K38" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="L38" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M38" t="n">
         <v>26</v>
       </c>
       <c r="N38" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -5556,7 +5570,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -5580,20 +5594,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>43.75</v>
+        <v>43.8667</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>2|16|19|37|44|49|26</t>
+          <t>14|17|19|30|41|44|26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39">
@@ -5624,28 +5638,28 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H39" t="n">
         <v>3</v>
       </c>
       <c r="I39" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J39" t="n">
         <v>23</v>
       </c>
       <c r="K39" t="n">
+        <v>34</v>
+      </c>
+      <c r="L39" t="n">
         <v>38</v>
       </c>
-      <c r="L39" t="n">
-        <v>44</v>
-      </c>
       <c r="M39" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="N39" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -5663,7 +5677,7 @@
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -5678,16 +5692,16 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>36.25</v>
+        <v>36.17439230769231</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>3|8|23|38|44|49|40</t>
+          <t>3|4|23|34|38|49|17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB39" t="n">
@@ -5725,25 +5739,25 @@
         <v>3</v>
       </c>
       <c r="H40" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I40" t="n">
+        <v>16</v>
+      </c>
+      <c r="J40" t="n">
         <v>19</v>
       </c>
-      <c r="J40" t="n">
-        <v>20</v>
-      </c>
       <c r="K40" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="L40" t="n">
         <v>44</v>
       </c>
       <c r="M40" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="N40" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -5752,7 +5766,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -5776,20 +5790,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>41.25</v>
+        <v>41.3667</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>7|19|20|30|44|45|15</t>
+          <t>2|16|19|37|44|49|24</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41">
@@ -5820,10 +5834,10 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H41" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I41" t="n">
         <v>15</v>
@@ -5832,7 +5846,7 @@
         <v>24</v>
       </c>
       <c r="K41" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L41" t="n">
         <v>34</v>
@@ -5841,7 +5855,7 @@
         <v>27</v>
       </c>
       <c r="N41" t="n">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -5850,7 +5864,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -5859,7 +5873,7 @@
         <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -5874,20 +5888,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>36.05769230769231</v>
+        <v>36.00955714285714</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>6|15|24|31|34|49|27</t>
+          <t>3|15|24|26|34|39|27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42">
@@ -5921,34 +5935,34 @@
         <v>4</v>
       </c>
       <c r="H42" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J42" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K42" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L42" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M42" t="n">
+        <v>6</v>
+      </c>
+      <c r="N42" t="n">
+        <v>143</v>
+      </c>
+      <c r="O42" t="n">
+        <v>3</v>
+      </c>
+      <c r="P42" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q42" t="n">
         <v>32</v>
-      </c>
-      <c r="N42" t="n">
-        <v>157</v>
-      </c>
-      <c r="O42" t="n">
-        <v>3</v>
-      </c>
-      <c r="P42" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>40</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -5972,20 +5986,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>39.75</v>
+        <v>39.8667</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>5|9|24|30|44|45|32</t>
+          <t>9|10|17|26|40|41|6</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43">
@@ -6025,19 +6039,19 @@
         <v>12</v>
       </c>
       <c r="J43" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K43" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L43" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M43" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="N43" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -6046,7 +6060,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -6070,20 +6084,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>35.75</v>
+        <v>35.8667</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>3|12|20|34|39|45|24</t>
+          <t>3|12|21|32|38|49|9</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44">
@@ -6117,25 +6131,25 @@
         <v>5</v>
       </c>
       <c r="H44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J44" t="n">
         <v>24</v>
       </c>
       <c r="K44" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L44" t="n">
+        <v>44</v>
+      </c>
+      <c r="M44" t="n">
         <v>31</v>
       </c>
-      <c r="M44" t="n">
-        <v>8</v>
-      </c>
       <c r="N44" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -6144,7 +6158,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -6168,16 +6182,16 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>38.75</v>
+        <v>38.8667</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>6|19|24|26|31|45|8</t>
+          <t>5|9|24|30|44|45|31</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB44" t="n">
@@ -6221,19 +6235,19 @@
         <v>6</v>
       </c>
       <c r="J45" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K45" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L45" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M45" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N45" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="O45" t="n">
         <v>3</v>
@@ -6242,7 +6256,7 @@
         <v>3</v>
       </c>
       <c r="Q45" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R45" t="n">
         <v>1</v>
@@ -6266,20 +6280,20 @@
         <v>5</v>
       </c>
       <c r="Y45" t="n">
-        <v>35.625</v>
+        <v>35.7417</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>3|6|9|34|38|49|10</t>
+          <t>3|6|20|31|44|45|1</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB45" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46">
@@ -6313,7 +6327,7 @@
         <v>6</v>
       </c>
       <c r="H46" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I46" t="n">
         <v>19</v>
@@ -6328,10 +6342,10 @@
         <v>31</v>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N46" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -6340,7 +6354,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -6364,20 +6378,20 @@
         <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>38.03571428571428</v>
+        <v>38.15241428571429</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17|19|24|26|31|46|4</t>
+          <t>6|19|24|26|31|45|7</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47">
@@ -6414,22 +6428,22 @@
         <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J47" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K47" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L47" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M47" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N47" t="n">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -6438,7 +6452,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -6462,20 +6476,20 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>35.51470588235294</v>
+        <v>35.63140588235294</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|17|24|37|38|46|49</t>
+          <t>3|6|19|38|40|49|47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48">
@@ -6509,25 +6523,25 @@
         <v>7</v>
       </c>
       <c r="H48" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I48" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K48" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="L48" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M48" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -6536,7 +6550,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -6560,20 +6574,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>37.5</v>
+        <v>37.6167</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16|17|24|33|38|41|12</t>
+          <t>9|18|19|30|44|45|3</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49">
@@ -6607,25 +6621,25 @@
         <v>17</v>
       </c>
       <c r="H49" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J49" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K49" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L49" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M49" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N49" t="n">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -6634,7 +6648,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -6658,20 +6672,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.41666666666666</v>
+        <v>35.53336666666667</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11|19|20|29|40|42|4</t>
+          <t>3|6|9|34|38|49|10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50">
@@ -6705,25 +6719,25 @@
         <v>8</v>
       </c>
       <c r="H50" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I50" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J50" t="n">
         <v>24</v>
       </c>
       <c r="K50" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="L50" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="M50" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="N50" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -6732,7 +6746,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -6756,20 +6770,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>37.08333333333333</v>
+        <v>37.20003333333333</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>2|9|24|40|43|45|33</t>
+          <t>16|17|24|33|38|41|4</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="51">
@@ -6806,22 +6820,22 @@
         <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="K51" t="n">
+        <v>32</v>
+      </c>
+      <c r="L51" t="n">
         <v>38</v>
       </c>
-      <c r="L51" t="n">
-        <v>44</v>
-      </c>
       <c r="M51" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N51" t="n">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -6854,16 +6868,16 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.32894736842105</v>
+        <v>35.44564736842106</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|4|11|38|44|49|1</t>
+          <t>3|20|23|32|38|49|12</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB51" t="n">
@@ -6901,22 +6915,22 @@
         <v>9</v>
       </c>
       <c r="H52" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I52" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J52" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K52" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="L52" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="M52" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N52" t="n">
         <v>163</v>
@@ -6928,7 +6942,7 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -6952,20 +6966,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>36.75</v>
+        <v>36.8667</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>6|16|19|37|41|44|7</t>
+          <t>17|19|24|26|31|46|4</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53">
@@ -6999,25 +7013,25 @@
         <v>19</v>
       </c>
       <c r="H53" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J53" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K53" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="L53" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M53" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="N53" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -7026,7 +7040,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -7050,20 +7064,20 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.25</v>
+        <v>35.3667</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10|19|20|28|35|45|5</t>
+          <t>3|17|24|37|38|46|49</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="54">
@@ -7097,25 +7111,25 @@
         <v>10</v>
       </c>
       <c r="H54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J54" t="n">
         <v>24</v>
       </c>
       <c r="K54" t="n">
+        <v>31</v>
+      </c>
+      <c r="L54" t="n">
+        <v>41</v>
+      </c>
+      <c r="M54" t="n">
         <v>30</v>
       </c>
-      <c r="L54" t="n">
-        <v>31</v>
-      </c>
-      <c r="M54" t="n">
-        <v>41</v>
-      </c>
       <c r="N54" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -7124,7 +7138,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -7148,20 +7162,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>36.47727272727273</v>
+        <v>36.59397272727273</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>3|19|24|30|31|40|41</t>
+          <t>2|9|24|31|41|44|30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="55">
@@ -7195,22 +7209,22 @@
         <v>20</v>
       </c>
       <c r="H55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I55" t="n">
+        <v>4</v>
+      </c>
+      <c r="J55" t="n">
         <v>11</v>
       </c>
-      <c r="J55" t="n">
-        <v>20</v>
-      </c>
       <c r="K55" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L55" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="M55" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N55" t="n">
         <v>149</v>
@@ -7222,7 +7236,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -7246,20 +7260,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>35.17857142857143</v>
+        <v>35.29527142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>5|11|20|32|37|44|12</t>
+          <t>3|4|11|38|44|49|1</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -7325,7 +7339,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -7339,10 +7353,10 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="G2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
@@ -7353,27 +7367,27 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="G3" t="n">
         <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="4">
@@ -7383,7 +7397,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
@@ -7420,20 +7434,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>2.75</v>
+        <v>2.8667</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5</v>
+        <v>0.2667</v>
       </c>
     </row>
   </sheetData>
@@ -7470,7 +7484,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12721</t>
+          <t>12728</t>
         </is>
       </c>
     </row>
@@ -7518,7 +7532,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-26 00:00:00</t>
+          <t>2026-05-27 00:00:00</t>
         </is>
       </c>
     </row>
@@ -7542,7 +7556,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-28 08:46:33</t>
+          <t>2026-05-28 17:12:22</t>
         </is>
       </c>
     </row>
@@ -7592,7 +7606,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UK49s: AntiCrowding_Recent50 is currently ranked first.</t>
+          <t>UK49s: Random_Baseline is currently ranked first.</t>
         </is>
       </c>
     </row>
@@ -7616,7 +7630,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2 model/game combinations are currently beating Random_Baseline.</t>
+          <t>0 model/game combinations are currently beating Random_Baseline.</t>
         </is>
       </c>
     </row>
@@ -7754,20 +7768,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>600</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7917</v>
+        <v>0.71</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.7167</v>
       </c>
       <c r="I2" t="n">
         <v>4</v>
@@ -7776,22 +7790,22 @@
         <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>2.75</v>
+        <v>2.8667</v>
       </c>
       <c r="L2" t="n">
-        <v>2.75</v>
+        <v>2.8667</v>
       </c>
       <c r="M2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="3">
@@ -7815,25 +7829,25 @@
         <v>600</v>
       </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8383</v>
+        <v>0.9367</v>
       </c>
       <c r="H3" t="n">
-        <v>0.86</v>
+        <v>0.9533</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6875</v>
+        <v>2.6667</v>
       </c>
       <c r="L3" t="n">
-        <v>2.625</v>
+        <v>2.6667</v>
       </c>
       <c r="M3" t="n">
         <v>15</v>
@@ -7842,10 +7856,10 @@
         <v>8</v>
       </c>
       <c r="O3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P3" t="n">
-        <v>0.625</v>
+        <v>0.5333</v>
       </c>
     </row>
     <row r="4">
@@ -7862,44 +7876,44 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>600</v>
       </c>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7017</v>
+        <v>0.6983</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7233000000000001</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>2.625</v>
+        <v>2.5333</v>
       </c>
       <c r="L4" t="n">
-        <v>2.4375</v>
+        <v>2.4667</v>
       </c>
       <c r="M4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5</v>
+        <v>0.4667</v>
       </c>
     </row>
     <row r="5">
@@ -7916,20 +7930,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>600</v>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6883</v>
+        <v>0.6967</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7117</v>
+        <v>0.7167</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
@@ -7938,22 +7952,22 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4375</v>
+        <v>2.4667</v>
       </c>
       <c r="L5" t="n">
-        <v>2.375</v>
+        <v>2.4</v>
       </c>
       <c r="M5" t="n">
         <v>15</v>
       </c>
       <c r="N5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>0.375</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="6">
@@ -7970,44 +7984,44 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_Recent50</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>600</v>
       </c>
       <c r="F6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7267</v>
+        <v>0.7133</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7467</v>
+        <v>0.7383</v>
       </c>
       <c r="I6" t="n">
         <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>2.375</v>
+        <v>2.4</v>
       </c>
       <c r="L6" t="n">
-        <v>2.3125</v>
+        <v>2.3333</v>
       </c>
       <c r="M6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N6" t="n">
         <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5</v>
+        <v>0.4667</v>
       </c>
     </row>
     <row r="7">
@@ -8024,20 +8038,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Weighted_Recent50</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>600</v>
       </c>
       <c r="F7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G7" t="n">
-        <v>0.72</v>
+        <v>0.745</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7367</v>
+        <v>0.7667</v>
       </c>
       <c r="I7" t="n">
         <v>4</v>
@@ -8046,10 +8060,10 @@
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>2.25</v>
+        <v>2.5333</v>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>2.3333</v>
       </c>
       <c r="M7" t="n">
         <v>14</v>
@@ -8058,10 +8072,10 @@
         <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3125</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8">
@@ -8070,7 +8084,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -8078,7 +8092,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -8088,10 +8102,10 @@
         <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>0.699</v>
+        <v>0.618</v>
       </c>
       <c r="H8" t="n">
-        <v>0.699</v>
+        <v>0.632</v>
       </c>
       <c r="I8" t="n">
         <v>3</v>
@@ -8100,19 +8114,23 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="M8" t="n">
         <v>74</v>
       </c>
       <c r="N8" t="n">
-        <v>16</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="O8" t="n">
+        <v>12</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -8124,7 +8142,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -8138,10 +8156,10 @@
         <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>0.671</v>
+        <v>0.613</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="I9" t="n">
         <v>3</v>
@@ -8153,19 +8171,19 @@
         <v>1.88</v>
       </c>
       <c r="L9" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="M9" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="N9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O9" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P9" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="10">
@@ -8174,15 +8192,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -8192,10 +8210,10 @@
         <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>0.596</v>
+        <v>0.678</v>
       </c>
       <c r="H10" t="n">
-        <v>0.612</v>
+        <v>0.678</v>
       </c>
       <c r="I10" t="n">
         <v>4</v>
@@ -8204,23 +8222,19 @@
         <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="L10" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="M10" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="N10" t="n">
-        <v>13</v>
-      </c>
-      <c r="O10" t="n">
-        <v>15</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.15</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -8228,15 +8242,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -8246,35 +8260,31 @@
         <v>100</v>
       </c>
       <c r="G11" t="n">
-        <v>0.658</v>
+        <v>0.779</v>
       </c>
       <c r="H11" t="n">
-        <v>0.676</v>
+        <v>0.779</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="L11" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="M11" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="N11" t="n">
-        <v>11</v>
-      </c>
-      <c r="O11" t="n">
-        <v>15</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.15</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -8286,11 +8296,11 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -8300,28 +8310,28 @@
         <v>100</v>
       </c>
       <c r="G12" t="n">
-        <v>0.753</v>
+        <v>0.71</v>
       </c>
       <c r="H12" t="n">
-        <v>0.753</v>
+        <v>0.71</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="L12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="M12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="N12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
@@ -8332,7 +8342,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -8340,7 +8350,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -8350,31 +8360,35 @@
         <v>100</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.632</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="L13" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="N13" t="n">
-        <v>10</v>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="O13" t="n">
+        <v>21</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.21</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -8382,7 +8396,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -8390,7 +8404,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -8400,19 +8414,19 @@
         <v>100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.704</v>
+        <v>0.616</v>
       </c>
       <c r="H14" t="n">
-        <v>0.704</v>
+        <v>0.637</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="L14" t="n">
         <v>1.7</v>
@@ -8421,10 +8435,14 @@
         <v>60</v>
       </c>
       <c r="N14" t="n">
-        <v>11</v>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="O14" t="n">
+        <v>17</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.17</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -8436,7 +8454,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -8450,34 +8468,34 @@
         <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6</v>
+        <v>0.584</v>
       </c>
       <c r="H15" t="n">
-        <v>0.612</v>
+        <v>0.599</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="L15" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="M15" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N15" t="n">
         <v>11</v>
       </c>
       <c r="O15" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="P15" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="16">
@@ -8486,15 +8504,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -8504,10 +8522,10 @@
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.616</v>
+        <v>0.676</v>
       </c>
       <c r="H16" t="n">
-        <v>0.632</v>
+        <v>0.676</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
@@ -8516,7 +8534,7 @@
         <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="L16" t="n">
         <v>1.66</v>
@@ -8527,12 +8545,8 @@
       <c r="N16" t="n">
         <v>9</v>
       </c>
-      <c r="O16" t="n">
-        <v>12</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0.12</v>
-      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -8540,11 +8554,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -8558,31 +8572,35 @@
         <v>100</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.576</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.588</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="L17" t="n">
         <v>1.65</v>
       </c>
       <c r="M17" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N17" t="n">
         <v>8</v>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>11</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.11</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -8590,15 +8608,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -8608,35 +8626,31 @@
         <v>100</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>0.614</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="M18" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="N18" t="n">
-        <v>6</v>
-      </c>
-      <c r="O18" t="n">
         <v>10</v>
       </c>
-      <c r="P18" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -8644,15 +8658,15 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -8662,35 +8676,31 @@
         <v>100</v>
       </c>
       <c r="G19" t="n">
-        <v>0.521</v>
+        <v>0.694</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.694</v>
       </c>
       <c r="I19" t="n">
         <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="L19" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="M19" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
-      </c>
-      <c r="O19" t="n">
-        <v>35</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0.35</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -8698,15 +8708,15 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -8716,31 +8726,35 @@
         <v>100</v>
       </c>
       <c r="G20" t="n">
-        <v>0.656</v>
+        <v>0.521</v>
       </c>
       <c r="H20" t="n">
-        <v>0.656</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
         <v>4</v>
       </c>
       <c r="K20" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="L20" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M20" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
-      </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="O20" t="n">
+        <v>35</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.35</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -9110,7 +9124,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -9132,35 +9146,35 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>0.699</v>
+        <v>0.678</v>
       </c>
       <c r="H2" t="n">
-        <v>0.699</v>
+        <v>0.678</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="L2" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="M2" t="n">
         <v>74</v>
       </c>
       <c r="N2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -9172,7 +9186,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -9182,10 +9196,10 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>0.671</v>
+        <v>0.618</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.632</v>
       </c>
       <c r="I3" t="n">
         <v>3</v>
@@ -9194,27 +9208,27 @@
         <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="L3" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="M3" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="N3" t="n">
         <v>11</v>
       </c>
       <c r="O3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P3" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -9280,20 +9294,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>600</v>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7917</v>
+        <v>0.71</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.7167</v>
       </c>
       <c r="I5" t="n">
         <v>4</v>
@@ -9302,22 +9316,22 @@
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>2.75</v>
+        <v>2.8667</v>
       </c>
       <c r="L5" t="n">
-        <v>2.75</v>
+        <v>2.8667</v>
       </c>
       <c r="M5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5</v>
+        <v>0.2667</v>
       </c>
     </row>
   </sheetData>
@@ -9383,10 +9397,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -9412,16 +9426,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.15</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -9437,20 +9451,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.18</v>
+        <v>-0.08</v>
       </c>
       <c r="F4" t="n">
-        <v>-6</v>
+        <v>4</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -9466,20 +9480,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="F5" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -9495,20 +9509,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="F6" t="n">
-        <v>-8</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -9524,20 +9538,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.32</v>
+        <v>-0.22</v>
       </c>
       <c r="F7" t="n">
-        <v>-8</v>
+        <v>4</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -9553,20 +9567,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="D8" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -9582,20 +9596,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="D9" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -9611,20 +9625,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="D10" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -9640,17 +9654,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="D11" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.12</v>
+        <v>-0.15</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -9669,20 +9683,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1.66</v>
       </c>
       <c r="D12" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.15</v>
+        <v>-0.19</v>
       </c>
       <c r="F12" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -9705,13 +9719,13 @@
         <v>1.65</v>
       </c>
       <c r="D13" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.16</v>
+        <v>-0.2</v>
       </c>
       <c r="F13" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -9901,24 +9915,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.75</v>
+        <v>2.8667</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4375</v>
+        <v>2.8667</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3125</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9934,20 +9948,20 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.625</v>
+        <v>2.6667</v>
       </c>
       <c r="D21" t="n">
-        <v>2.4375</v>
+        <v>2.8667</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1875</v>
+        <v>-0.2</v>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9959,20 +9973,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.4375</v>
+        <v>2.4667</v>
       </c>
       <c r="D22" t="n">
-        <v>2.4375</v>
+        <v>2.8667</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -9988,20 +10002,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2.375</v>
+        <v>2.4</v>
       </c>
       <c r="D23" t="n">
-        <v>2.4375</v>
+        <v>2.8667</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0625</v>
+        <v>-0.4667</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -10017,20 +10031,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_Recent50</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.3125</v>
+        <v>2.3333</v>
       </c>
       <c r="D24" t="n">
-        <v>2.4375</v>
+        <v>2.8667</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.125</v>
+        <v>-0.5334</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -10046,20 +10060,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Weighted_Recent50</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.25</v>
+        <v>2.3333</v>
       </c>
       <c r="D25" t="n">
-        <v>2.4375</v>
+        <v>2.8667</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1875</v>
+        <v>-0.5334</v>
       </c>
       <c r="F25" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>

--- a/data/exports/reporting/daily_lottery_summary.xlsx
+++ b/data/exports/reporting/daily_lottery_summary.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:52</t>
+          <t>2026-05-28 19:50:13</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr"/>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB23" t="n">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB35" t="n">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB36" t="n">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB37" t="n">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB38" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB39" t="n">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB40" t="n">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB41" t="n">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB42" t="n">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB43" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB44" t="n">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB48" t="n">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB49" t="n">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB50" t="n">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB51" t="n">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB52" t="n">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB55" t="n">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-28 17:12:22</t>
+          <t>2026-05-28 19:42:06</t>
         </is>
       </c>
     </row>
